--- a/backend/tracked_jobs.xlsx
+++ b/backend/tracked_jobs.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Job Tracker" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Job Tracker'!$A$1:$H$314</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Job Tracker'!$A$1:$H$465</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -543,7 +543,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H314"/>
+  <dimension ref="A1:H465"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -13071,30 +13071,30 @@
       </c>
     </row>
     <row r="314" ht="28" customHeight="1">
-      <c r="A314" s="3" t="inlineStr">
+      <c r="A314" s="12" t="inlineStr">
         <is>
           <t>Engineering Intern (Summer 2026)</t>
         </is>
       </c>
-      <c r="B314" s="4" t="inlineStr">
+      <c r="B314" s="13" t="inlineStr">
         <is>
           <t>Olivia</t>
         </is>
       </c>
-      <c r="C314" s="5" t="inlineStr">
+      <c r="C314" s="14" t="inlineStr">
         <is>
           <t>https://fedex.paradox.ai/co/FederalExpressCorporation41/J...</t>
         </is>
       </c>
-      <c r="D314" s="6" t="inlineStr">
-        <is>
-          <t>shortlisted</t>
-        </is>
-      </c>
-      <c r="E314" s="4" t="n">
+      <c r="D314" s="13" t="inlineStr">
+        <is>
+          <t>tailored</t>
+        </is>
+      </c>
+      <c r="E314" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="F314" s="4" t="inlineStr">
+      <c r="F314" s="13" t="inlineStr">
         <is>
           <t>Starting score: 10/10
 STEP 1: Auto-reject
@@ -13115,15 +13115,6047 @@
 - Total score: 10 - 2 - 4 + 1 + 1 = 6</t>
         </is>
       </c>
-      <c r="G314" s="4" t="inlineStr"/>
+      <c r="G314" s="13" t="inlineStr"/>
       <c r="H314" s="7" t="inlineStr">
         <is>
           <t>➜ Apply</t>
         </is>
       </c>
     </row>
+    <row r="315" ht="28" customHeight="1">
+      <c r="A315" s="8" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B315" s="9" t="inlineStr">
+        <is>
+          <t>Alarm.com</t>
+        </is>
+      </c>
+      <c r="C315" s="10" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/alarmcom/jobs/8417037002</t>
+        </is>
+      </c>
+      <c r="D315" s="11" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="E315" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F315" s="9" t="inlineStr">
+        <is>
+          <t>The job is for a Software Engineer Intern, which matches the candidate's target roles. The candidate has relevant skills in Full Stack Development, AI Agents, LLM pipelines, Machine Learning, and Software Engineering. However, the job explicitly requires sponsorship, which the candidate needs, resulting in an auto-reject. The job does not require 5+ years of experience, so no deductions apply for experience gap. There are no core tech stack mismatches. The domain is in software engineering, so no domain penalty applies. The candidate's experience level is an internship, which aligns with the job requirements.</t>
+        </is>
+      </c>
+      <c r="G315" s="9" t="inlineStr">
+        <is>
+          <t>2026-03-07T02:20:26.162268</t>
+        </is>
+      </c>
+      <c r="H315" s="7" t="inlineStr">
+        <is>
+          <t>➜ Apply</t>
+        </is>
+      </c>
+    </row>
+    <row r="316" ht="28" customHeight="1">
+      <c r="A316" s="3" t="inlineStr">
+        <is>
+          <t>Intern - Enterprise Metadata Management</t>
+        </is>
+      </c>
+      <c r="B316" s="4" t="inlineStr">
+        <is>
+          <t>PBS</t>
+        </is>
+      </c>
+      <c r="C316" s="5" t="inlineStr">
+        <is>
+          <t>https://vhr-pbs.wd5.myworkdayjobs.com/PBSCareers/job/Alex...</t>
+        </is>
+      </c>
+      <c r="D316" s="6" t="inlineStr">
+        <is>
+          <t>shortlisted</t>
+        </is>
+      </c>
+      <c r="E316" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="F316" s="4" t="inlineStr">
+        <is>
+          <t>The job is explicitly for an Intern position, so there is no experience gap. The candidate's skills and experience align well with the required technologies, and the job does not fall into any of the auto-reject categories. The candidate's preferences and visa status do not affect the score as the job is an internship. The candidate's experience and skills are relevant to the job, and there is no domain penalty.</t>
+        </is>
+      </c>
+      <c r="G316" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-07T02:20:26.163265</t>
+        </is>
+      </c>
+      <c r="H316" s="7" t="inlineStr">
+        <is>
+          <t>➜ Apply</t>
+        </is>
+      </c>
+    </row>
+    <row r="317" ht="28" customHeight="1">
+      <c r="A317" s="8" t="inlineStr">
+        <is>
+          <t>Research Scientist Intern - Text Data Research</t>
+        </is>
+      </c>
+      <c r="B317" s="9" t="inlineStr">
+        <is>
+          <t>Meta</t>
+        </is>
+      </c>
+      <c r="C317" s="10" t="inlineStr">
+        <is>
+          <t>https://www.metacareers.com/jobs/1183817733250704</t>
+        </is>
+      </c>
+      <c r="D317" s="11" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="E317" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F317" s="9" t="inlineStr">
+        <is>
+          <t>Rejected: Found dealbreaker terms in JD (phd)</t>
+        </is>
+      </c>
+      <c r="G317" s="9" t="inlineStr">
+        <is>
+          <t>2026-03-07T02:20:26.164264</t>
+        </is>
+      </c>
+      <c r="H317" s="7" t="inlineStr">
+        <is>
+          <t>➜ Apply</t>
+        </is>
+      </c>
+    </row>
+    <row r="318" ht="28" customHeight="1">
+      <c r="A318" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineer Intern/Co-op</t>
+        </is>
+      </c>
+      <c r="B318" s="4" t="inlineStr">
+        <is>
+          <t>KION Group</t>
+        </is>
+      </c>
+      <c r="C318" s="5" t="inlineStr">
+        <is>
+          <t>https://kiongroup.wd3.myworkdayjobs.com/en-US/KION_SCS/jo...</t>
+        </is>
+      </c>
+      <c r="D318" s="6" t="inlineStr">
+        <is>
+          <t>shortlisted</t>
+        </is>
+      </c>
+      <c r="E318" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="F318" s="4" t="inlineStr">
+        <is>
+          <t>Auto-Shortlisted (Protected Title)</t>
+        </is>
+      </c>
+      <c r="G318" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-07T02:20:26.164264</t>
+        </is>
+      </c>
+      <c r="H318" s="7" t="inlineStr">
+        <is>
+          <t>➜ Apply</t>
+        </is>
+      </c>
+    </row>
+    <row r="319" ht="28" customHeight="1">
+      <c r="A319" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineer Intern</t>
+        </is>
+      </c>
+      <c r="B319" s="4" t="inlineStr">
+        <is>
+          <t>CACI</t>
+        </is>
+      </c>
+      <c r="C319" s="5" t="inlineStr">
+        <is>
+          <t>https://caci.wd1.myworkdayjobs.com/external/job/US-VA-Ash...</t>
+        </is>
+      </c>
+      <c r="D319" s="6" t="inlineStr">
+        <is>
+          <t>shortlisted</t>
+        </is>
+      </c>
+      <c r="E319" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="F319" s="4" t="inlineStr">
+        <is>
+          <t>Auto-Shortlisted (Protected Title)</t>
+        </is>
+      </c>
+      <c r="G319" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-07T02:20:26.164264</t>
+        </is>
+      </c>
+      <c r="H319" s="7" t="inlineStr">
+        <is>
+          <t>➜ Apply</t>
+        </is>
+      </c>
+    </row>
+    <row r="320" ht="28" customHeight="1">
+      <c r="A320" s="8" t="inlineStr">
+        <is>
+          <t>Research Scientist Intern - MSL Infra Kernels &amp; Optimizations</t>
+        </is>
+      </c>
+      <c r="B320" s="9" t="inlineStr">
+        <is>
+          <t>Meta</t>
+        </is>
+      </c>
+      <c r="C320" s="10" t="inlineStr">
+        <is>
+          <t>https://www.metacareers.com/jobs/4342539279351100</t>
+        </is>
+      </c>
+      <c r="D320" s="11" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="E320" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F320" s="9" t="inlineStr">
+        <is>
+          <t>Rejected: Found dealbreaker terms in JD (phd)</t>
+        </is>
+      </c>
+      <c r="G320" s="9" t="inlineStr">
+        <is>
+          <t>2026-03-07T02:20:26.164264</t>
+        </is>
+      </c>
+      <c r="H320" s="7" t="inlineStr">
+        <is>
+          <t>➜ Apply</t>
+        </is>
+      </c>
+    </row>
+    <row r="321" ht="28" customHeight="1">
+      <c r="A321" s="3" t="inlineStr">
+        <is>
+          <t>DL Gen AI Intern</t>
+        </is>
+      </c>
+      <c r="B321" s="4" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="C321" s="5" t="inlineStr">
+        <is>
+          <t>https://sec.wd3.myworkdayjobs.com/Samsung_Careers/job/645...</t>
+        </is>
+      </c>
+      <c r="D321" s="6" t="inlineStr">
+        <is>
+          <t>shortlisted</t>
+        </is>
+      </c>
+      <c r="E321" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="F321" s="4" t="inlineStr">
+        <is>
+          <t>Auto-Shortlisted (Protected Title)</t>
+        </is>
+      </c>
+      <c r="G321" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-07T02:20:26.164264</t>
+        </is>
+      </c>
+      <c r="H321" s="7" t="inlineStr">
+        <is>
+          <t>➜ Apply</t>
+        </is>
+      </c>
+    </row>
+    <row r="322" ht="28" customHeight="1">
+      <c r="A322" s="3" t="inlineStr">
+        <is>
+          <t>Intern - Data Analytics</t>
+        </is>
+      </c>
+      <c r="B322" s="4" t="inlineStr">
+        <is>
+          <t>Commonwealth of Massachusetts</t>
+        </is>
+      </c>
+      <c r="C322" s="5" t="inlineStr">
+        <is>
+          <t>https://massanf.taleo.net/careersection/ex/jobdetail.ftl?...</t>
+        </is>
+      </c>
+      <c r="D322" s="6" t="inlineStr">
+        <is>
+          <t>shortlisted</t>
+        </is>
+      </c>
+      <c r="E322" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="F322" s="4" t="inlineStr">
+        <is>
+          <t>The job is explicitly for an Intern - Data Analytics position, which matches the candidate's preference for an internship. The job does not explicitly require US Citizenship or a Security Clearance. The job does not specify a senior or staff level, so no auto-reject applies. The job requires 3-4 years of experience, which deducts -2. The job does not mention any specific core tech stack mismatch, so no deductions apply. The job is in the public sector, which does not apply the domain penalty. The role title does not exactly match the candidate's target roles, so no bonus applies. The final score is 8, which is above the candidate's score threshold of 6, and the candidate is an intern, so no keyword weaving is necessary.</t>
+        </is>
+      </c>
+      <c r="G322" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-07T02:20:26.164264</t>
+        </is>
+      </c>
+      <c r="H322" s="7" t="inlineStr">
+        <is>
+          <t>➜ Apply</t>
+        </is>
+      </c>
+    </row>
+    <row r="323" ht="28" customHeight="1">
+      <c r="A323" s="8" t="inlineStr">
+        <is>
+          <t>Manufacturing Design Engineer Intern</t>
+        </is>
+      </c>
+      <c r="B323" s="9" t="inlineStr">
+        <is>
+          <t>Skydio</t>
+        </is>
+      </c>
+      <c r="C323" s="10" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/skydio/5d12ad64-c439-4ee3-947c-d...</t>
+        </is>
+      </c>
+      <c r="D323" s="11" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="E323" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F323" s="9" t="inlineStr">
+        <is>
+          <t>The job is explicitly for a Manufacturing Design Engineer Intern, which does not match the candidate's target roles. The job description does not require any specific programming or AI/ML skills, and the candidate's experience is primarily in software engineering and AI/ML, which are not relevant to the job. The candidate is also required to be a US citizen or have a valid work authorization, which the candidate does not meet.</t>
+        </is>
+      </c>
+      <c r="G323" s="9" t="inlineStr">
+        <is>
+          <t>2026-03-07T02:20:26.164264</t>
+        </is>
+      </c>
+      <c r="H323" s="7" t="inlineStr">
+        <is>
+          <t>➜ Apply</t>
+        </is>
+      </c>
+    </row>
+    <row r="324" ht="28" customHeight="1">
+      <c r="A324" s="8" t="inlineStr">
+        <is>
+          <t>Research Scientist Intern - MSL Infra Kernels &amp; Optimizations</t>
+        </is>
+      </c>
+      <c r="B324" s="9" t="inlineStr">
+        <is>
+          <t>Meta</t>
+        </is>
+      </c>
+      <c r="C324" s="10" t="inlineStr">
+        <is>
+          <t>https://www.metacareers.com/jobs/1901750214551007</t>
+        </is>
+      </c>
+      <c r="D324" s="11" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="E324" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F324" s="9" t="inlineStr">
+        <is>
+          <t>Rejected: Non-US Location (London, UK)</t>
+        </is>
+      </c>
+      <c r="G324" s="9" t="inlineStr">
+        <is>
+          <t>2026-03-07T02:20:26.164264</t>
+        </is>
+      </c>
+      <c r="H324" s="7" t="inlineStr">
+        <is>
+          <t>➜ Apply</t>
+        </is>
+      </c>
+    </row>
+    <row r="325" ht="28" customHeight="1">
+      <c r="A325" s="3" t="inlineStr">
+        <is>
+          <t>Computer Vision Data Intern</t>
+        </is>
+      </c>
+      <c r="B325" s="4" t="inlineStr">
+        <is>
+          <t>Glimpse Engineering</t>
+        </is>
+      </c>
+      <c r="C325" s="5" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/glimp-se/c9b277ee-5355-42a4-b050...</t>
+        </is>
+      </c>
+      <c r="D325" s="6" t="inlineStr">
+        <is>
+          <t>shortlisted</t>
+        </is>
+      </c>
+      <c r="E325" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="F325" s="4" t="inlineStr">
+        <is>
+          <t>The job is explicitly for a Computer Vision Data Intern, which is an internship. The candidate is currently enrolled in a Master of Computer Science program and has relevant experience in Full Stack Development, AI Agents, and Machine Learning. However, the job requires on-site work, which the candidate is open to but may need to relocate for. The job does not explicitly require 5+ years of experience, so no deductions are applied for experience. There is no mention of a core tech stack mismatch, and the domain is not in a non-tech company, finance, or legal tech, so no domain penalties apply. The candidate's role does not exactly match the job title, but it is close enough that no bonus is added.</t>
+        </is>
+      </c>
+      <c r="G325" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-07T02:20:26.164264</t>
+        </is>
+      </c>
+      <c r="H325" s="7" t="inlineStr">
+        <is>
+          <t>➜ Apply</t>
+        </is>
+      </c>
+    </row>
+    <row r="326" ht="28" customHeight="1">
+      <c r="A326" s="8" t="inlineStr">
+        <is>
+          <t>Research Scientist Intern - Voice Modeling Team</t>
+        </is>
+      </c>
+      <c r="B326" s="9" t="inlineStr">
+        <is>
+          <t>Meta</t>
+        </is>
+      </c>
+      <c r="C326" s="10" t="inlineStr">
+        <is>
+          <t>https://www.metacareers.com/jobs/1523439395527958</t>
+        </is>
+      </c>
+      <c r="D326" s="11" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="E326" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F326" s="9" t="inlineStr">
+        <is>
+          <t>Rejected: Non-US Location (London, UK)</t>
+        </is>
+      </c>
+      <c r="G326" s="9" t="inlineStr">
+        <is>
+          <t>2026-03-07T02:20:26.164264</t>
+        </is>
+      </c>
+      <c r="H326" s="7" t="inlineStr">
+        <is>
+          <t>➜ Apply</t>
+        </is>
+      </c>
+    </row>
+    <row r="327" ht="28" customHeight="1">
+      <c r="A327" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineer Intern</t>
+        </is>
+      </c>
+      <c r="B327" s="4" t="inlineStr">
+        <is>
+          <t>Tatari</t>
+        </is>
+      </c>
+      <c r="C327" s="5" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/tatari/jobs/8451505002</t>
+        </is>
+      </c>
+      <c r="D327" s="6" t="inlineStr">
+        <is>
+          <t>shortlisted</t>
+        </is>
+      </c>
+      <c r="E327" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="F327" s="4" t="inlineStr">
+        <is>
+          <t>Auto-Shortlisted (Protected Title)</t>
+        </is>
+      </c>
+      <c r="G327" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-07T02:20:26.164264</t>
+        </is>
+      </c>
+      <c r="H327" s="7" t="inlineStr">
+        <is>
+          <t>➜ Apply</t>
+        </is>
+      </c>
+    </row>
+    <row r="328" ht="28" customHeight="1">
+      <c r="A328" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineer Intern</t>
+        </is>
+      </c>
+      <c r="B328" s="4" t="inlineStr">
+        <is>
+          <t>Tatari</t>
+        </is>
+      </c>
+      <c r="C328" s="5" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/tatari/jobs/8451506002</t>
+        </is>
+      </c>
+      <c r="D328" s="6" t="inlineStr">
+        <is>
+          <t>shortlisted</t>
+        </is>
+      </c>
+      <c r="E328" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="F328" s="4" t="inlineStr">
+        <is>
+          <t>Auto-Shortlisted (Protected Title)</t>
+        </is>
+      </c>
+      <c r="G328" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-07T02:20:26.164264</t>
+        </is>
+      </c>
+      <c r="H328" s="7" t="inlineStr">
+        <is>
+          <t>➜ Apply</t>
+        </is>
+      </c>
+    </row>
+    <row r="329" ht="28" customHeight="1">
+      <c r="A329" s="8" t="inlineStr">
+        <is>
+          <t>Research Scientist Intern</t>
+        </is>
+      </c>
+      <c r="B329" s="9" t="inlineStr">
+        <is>
+          <t>Meta</t>
+        </is>
+      </c>
+      <c r="C329" s="10" t="inlineStr">
+        <is>
+          <t>https://www.metacareers.com/jobs/1445688106951654</t>
+        </is>
+      </c>
+      <c r="D329" s="11" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="E329" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F329" s="9" t="inlineStr">
+        <is>
+          <t>Rejected: Found dealbreaker terms in JD (phd)</t>
+        </is>
+      </c>
+      <c r="G329" s="9" t="inlineStr">
+        <is>
+          <t>2026-03-07T02:20:26.164264</t>
+        </is>
+      </c>
+      <c r="H329" s="7" t="inlineStr">
+        <is>
+          <t>➜ Apply</t>
+        </is>
+      </c>
+    </row>
+    <row r="330" ht="28" customHeight="1">
+      <c r="A330" s="3" t="inlineStr">
+        <is>
+          <t>Software Developer Intern</t>
+        </is>
+      </c>
+      <c r="B330" s="4" t="inlineStr">
+        <is>
+          <t>ASSA ABLOY</t>
+        </is>
+      </c>
+      <c r="C330" s="5" t="inlineStr">
+        <is>
+          <t>https://assaabloy.jobs2web.com/job/New-Haven-Software-Dev...</t>
+        </is>
+      </c>
+      <c r="D330" s="6" t="inlineStr">
+        <is>
+          <t>shortlisted</t>
+        </is>
+      </c>
+      <c r="E330" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="F330" s="4" t="inlineStr">
+        <is>
+          <t>The job does not explicitly require US Citizenship or Security Clearance, so no auto-reject. The job is an internship, which is within the candidate's preference, so no experience gap deduction. The job requires foundational knowledge of C#, Python, and .NET Framework/Core, which the candidate has through academic, internship, or personal project experience. The job also requires exposure to Azure cloud services and CI/CD concepts, which the candidate has basic familiarity with. The job is in the IT domain, so no domain penalty. The role title matches the candidate's target roles, so a +1 is added. The final score is 8, which meets the candidate's score threshold of 6.</t>
+        </is>
+      </c>
+      <c r="G330" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-07T02:20:26.164264</t>
+        </is>
+      </c>
+      <c r="H330" s="7" t="inlineStr">
+        <is>
+          <t>➜ Apply</t>
+        </is>
+      </c>
+    </row>
+    <row r="331" ht="28" customHeight="1">
+      <c r="A331" s="8" t="inlineStr">
+        <is>
+          <t>Research Scientist Intern - Pytorch On-Device</t>
+        </is>
+      </c>
+      <c r="B331" s="9" t="inlineStr">
+        <is>
+          <t>Meta</t>
+        </is>
+      </c>
+      <c r="C331" s="10" t="inlineStr">
+        <is>
+          <t>https://www.metacareers.com/jobs/1401444685044473</t>
+        </is>
+      </c>
+      <c r="D331" s="11" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="E331" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F331" s="9" t="inlineStr">
+        <is>
+          <t>Rejected: Found dealbreaker terms in JD (phd)</t>
+        </is>
+      </c>
+      <c r="G331" s="9" t="inlineStr">
+        <is>
+          <t>2026-03-07T02:20:26.164264</t>
+        </is>
+      </c>
+      <c r="H331" s="7" t="inlineStr">
+        <is>
+          <t>➜ Apply</t>
+        </is>
+      </c>
+    </row>
+    <row r="332" ht="28" customHeight="1">
+      <c r="A332" s="8" t="inlineStr">
+        <is>
+          <t>Research Scientist Intern - Meta Recommendation Systems - PhD</t>
+        </is>
+      </c>
+      <c r="B332" s="9" t="inlineStr">
+        <is>
+          <t>Meta</t>
+        </is>
+      </c>
+      <c r="C332" s="10" t="inlineStr">
+        <is>
+          <t>https://www.metacareers.com/jobs/887534076970830</t>
+        </is>
+      </c>
+      <c r="D332" s="11" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="E332" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F332" s="9" t="inlineStr">
+        <is>
+          <t>Rejected: Found dealbreaker terms in JD (ph.d)</t>
+        </is>
+      </c>
+      <c r="G332" s="9" t="inlineStr">
+        <is>
+          <t>2026-03-07T02:20:26.164264</t>
+        </is>
+      </c>
+      <c r="H332" s="7" t="inlineStr">
+        <is>
+          <t>➜ Apply</t>
+        </is>
+      </c>
+    </row>
+    <row r="333" ht="28" customHeight="1">
+      <c r="A333" s="8" t="inlineStr">
+        <is>
+          <t>Research Scientist Intern - Multimodal AI</t>
+        </is>
+      </c>
+      <c r="B333" s="9" t="inlineStr">
+        <is>
+          <t>Meta</t>
+        </is>
+      </c>
+      <c r="C333" s="10" t="inlineStr">
+        <is>
+          <t>https://www.metacareers.com/jobs/2082160555965742</t>
+        </is>
+      </c>
+      <c r="D333" s="11" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="E333" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F333" s="9" t="inlineStr">
+        <is>
+          <t>Rejected: Found dealbreaker terms in JD (phd)</t>
+        </is>
+      </c>
+      <c r="G333" s="9" t="inlineStr">
+        <is>
+          <t>2026-03-07T02:20:26.164264</t>
+        </is>
+      </c>
+      <c r="H333" s="7" t="inlineStr">
+        <is>
+          <t>➜ Apply</t>
+        </is>
+      </c>
+    </row>
+    <row r="334" ht="28" customHeight="1">
+      <c r="A334" s="3" t="inlineStr">
+        <is>
+          <t>Data Engineering Intern - Congressional Data</t>
+        </is>
+      </c>
+      <c r="B334" s="4" t="inlineStr">
+        <is>
+          <t>Sunwater Capital</t>
+        </is>
+      </c>
+      <c r="C334" s="5" t="inlineStr">
+        <is>
+          <t>https://jobs.lever.co/sunwatercapital/51139004-df7d-409e-...</t>
+        </is>
+      </c>
+      <c r="D334" s="6" t="inlineStr">
+        <is>
+          <t>shortlisted</t>
+        </is>
+      </c>
+      <c r="E334" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="F334" s="4" t="inlineStr">
+        <is>
+          <t>The job is explicitly for an Intern, which does not trigger the auto-reject. The candidate has relevant experience in Full Stack Development, AI Agents, LLM pipelines, and Machine Learning, which aligns with the core tech stack required for a Data Engineering Intern role. The candidate's current location is not specified, but the job is open to remote, which is acceptable. The candidate requires sponsorship, which is noted but does not auto-reject the application. The candidate's experience level is consistent with an intern role, and the job does not require 5+ years of experience, so no experience gap deduction applies.</t>
+        </is>
+      </c>
+      <c r="G334" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-07T02:20:26.164264</t>
+        </is>
+      </c>
+      <c r="H334" s="7" t="inlineStr">
+        <is>
+          <t>➜ Apply</t>
+        </is>
+      </c>
+    </row>
+    <row r="335" ht="28" customHeight="1">
+      <c r="A335" s="8" t="inlineStr">
+        <is>
+          <t>Research Scientist - Novel Organic Materials</t>
+        </is>
+      </c>
+      <c r="B335" s="9" t="inlineStr">
+        <is>
+          <t>Meta</t>
+        </is>
+      </c>
+      <c r="C335" s="10" t="inlineStr">
+        <is>
+          <t>https://www.metacareers.com/jobs/884653154471172</t>
+        </is>
+      </c>
+      <c r="D335" s="11" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="E335" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F335" s="9" t="inlineStr">
+        <is>
+          <t>Rejected: Found dealbreaker terms in JD (phd)</t>
+        </is>
+      </c>
+      <c r="G335" s="9" t="inlineStr">
+        <is>
+          <t>2026-03-07T02:20:26.164264</t>
+        </is>
+      </c>
+      <c r="H335" s="7" t="inlineStr">
+        <is>
+          <t>➜ Apply</t>
+        </is>
+      </c>
+    </row>
+    <row r="336" ht="28" customHeight="1">
+      <c r="A336" s="3" t="inlineStr">
+        <is>
+          <t>Quality &amp; Data Analytics Co-op</t>
+        </is>
+      </c>
+      <c r="B336" s="4" t="inlineStr">
+        <is>
+          <t>Rolls Royce</t>
+        </is>
+      </c>
+      <c r="C336" s="5" t="inlineStr">
+        <is>
+          <t>https://jobs.bmwgroup.com/job/Spartanburg-Quality-&amp;-Data-...</t>
+        </is>
+      </c>
+      <c r="D336" s="6" t="inlineStr">
+        <is>
+          <t>shortlisted</t>
+        </is>
+      </c>
+      <c r="E336" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="F336" s="4" t="inlineStr">
+        <is>
+          <t>The job is explicitly for an intern position, so no deductions apply under EXPERIENCE GAP. The job does not require US Citizenship or Security Clearance, so no deductions apply under AUTO-REJECT. The job is not in a domain that incurs a penalty, such as finance or legal tech. The job requires an engineering degree, which is not a core tech stack mismatch. The job title does not exactly match the candidate's target roles, but it is close, so no bonus is added. The candidate's skills and experience align well with the job requirements, particularly in data analytics, problem-solving, and software development. The candidate's GPA and enrollment status meet the job's requirements.</t>
+        </is>
+      </c>
+      <c r="G336" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-07T02:20:26.164264</t>
+        </is>
+      </c>
+      <c r="H336" s="7" t="inlineStr">
+        <is>
+          <t>➜ Apply</t>
+        </is>
+      </c>
+    </row>
+    <row r="337" ht="28" customHeight="1">
+      <c r="A337" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineer Intern</t>
+        </is>
+      </c>
+      <c r="B337" s="4" t="inlineStr">
+        <is>
+          <t>Tatari</t>
+        </is>
+      </c>
+      <c r="C337" s="5" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/tatari/jobs/8451504002</t>
+        </is>
+      </c>
+      <c r="D337" s="6" t="inlineStr">
+        <is>
+          <t>shortlisted</t>
+        </is>
+      </c>
+      <c r="E337" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="F337" s="4" t="inlineStr">
+        <is>
+          <t>Auto-Shortlisted (Protected Title)</t>
+        </is>
+      </c>
+      <c r="G337" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-07T02:20:26.164264</t>
+        </is>
+      </c>
+      <c r="H337" s="7" t="inlineStr">
+        <is>
+          <t>➜ Apply</t>
+        </is>
+      </c>
+    </row>
+    <row r="338" ht="28" customHeight="1">
+      <c r="A338" s="8" t="inlineStr">
+        <is>
+          <t>Research Scientist Intern - Agentic AI</t>
+        </is>
+      </c>
+      <c r="B338" s="9" t="inlineStr">
+        <is>
+          <t>Meta</t>
+        </is>
+      </c>
+      <c r="C338" s="10" t="inlineStr">
+        <is>
+          <t>https://www.metacareers.com/jobs/1505624153994969</t>
+        </is>
+      </c>
+      <c r="D338" s="11" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="E338" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F338" s="9" t="inlineStr">
+        <is>
+          <t>Rejected: Found dealbreaker terms in JD (ph.d)</t>
+        </is>
+      </c>
+      <c r="G338" s="9" t="inlineStr">
+        <is>
+          <t>2026-03-07T02:20:26.164264</t>
+        </is>
+      </c>
+      <c r="H338" s="7" t="inlineStr">
+        <is>
+          <t>➜ Apply</t>
+        </is>
+      </c>
+    </row>
+    <row r="339" ht="28" customHeight="1">
+      <c r="A339" s="8" t="inlineStr">
+        <is>
+          <t>Research Scientist Intern - Applied Vision - PhD</t>
+        </is>
+      </c>
+      <c r="B339" s="9" t="inlineStr">
+        <is>
+          <t>Meta</t>
+        </is>
+      </c>
+      <c r="C339" s="10" t="inlineStr">
+        <is>
+          <t>https://www.metacareers.com/jobs/1112761774275681</t>
+        </is>
+      </c>
+      <c r="D339" s="11" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="E339" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F339" s="9" t="inlineStr">
+        <is>
+          <t>Rejected: Found dealbreaker terms in JD (phd)</t>
+        </is>
+      </c>
+      <c r="G339" s="9" t="inlineStr">
+        <is>
+          <t>2026-03-07T02:20:26.164264</t>
+        </is>
+      </c>
+      <c r="H339" s="7" t="inlineStr">
+        <is>
+          <t>➜ Apply</t>
+        </is>
+      </c>
+    </row>
+    <row r="340" ht="28" customHeight="1">
+      <c r="A340" s="8" t="inlineStr">
+        <is>
+          <t>Research Scientist Intern - PyTorch Distributed - PhD</t>
+        </is>
+      </c>
+      <c r="B340" s="9" t="inlineStr">
+        <is>
+          <t>Meta</t>
+        </is>
+      </c>
+      <c r="C340" s="10" t="inlineStr">
+        <is>
+          <t>https://www.metacareers.com/jobs/1804141453635398</t>
+        </is>
+      </c>
+      <c r="D340" s="11" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="E340" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F340" s="9" t="inlineStr">
+        <is>
+          <t>Rejected: Found dealbreaker terms in JD (phd)</t>
+        </is>
+      </c>
+      <c r="G340" s="9" t="inlineStr">
+        <is>
+          <t>2026-03-07T02:20:26.164264</t>
+        </is>
+      </c>
+      <c r="H340" s="7" t="inlineStr">
+        <is>
+          <t>➜ Apply</t>
+        </is>
+      </c>
+    </row>
+    <row r="341" ht="28" customHeight="1">
+      <c r="A341" s="8" t="inlineStr">
+        <is>
+          <t>Research Scientist Intern - Msl</t>
+        </is>
+      </c>
+      <c r="B341" s="9" t="inlineStr">
+        <is>
+          <t>Meta</t>
+        </is>
+      </c>
+      <c r="C341" s="10" t="inlineStr">
+        <is>
+          <t>https://www.metacareers.com/jobs/1974267053433921</t>
+        </is>
+      </c>
+      <c r="D341" s="11" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="E341" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F341" s="9" t="inlineStr">
+        <is>
+          <t>Rejected: Found dealbreaker terms in JD (ph.d)</t>
+        </is>
+      </c>
+      <c r="G341" s="9" t="inlineStr">
+        <is>
+          <t>2026-03-07T02:20:26.164264</t>
+        </is>
+      </c>
+      <c r="H341" s="7" t="inlineStr">
+        <is>
+          <t>➜ Apply</t>
+        </is>
+      </c>
+    </row>
+    <row r="342" ht="28" customHeight="1">
+      <c r="A342" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineer Intern</t>
+        </is>
+      </c>
+      <c r="B342" s="4" t="inlineStr">
+        <is>
+          <t>Peraton</t>
+        </is>
+      </c>
+      <c r="C342" s="5" t="inlineStr">
+        <is>
+          <t>https://careers-peraton.icims.com/jobs/164209/job?mobile=...</t>
+        </is>
+      </c>
+      <c r="D342" s="6" t="inlineStr">
+        <is>
+          <t>shortlisted</t>
+        </is>
+      </c>
+      <c r="E342" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="F342" s="4" t="inlineStr">
+        <is>
+          <t>Auto-Shortlisted (Protected Title)</t>
+        </is>
+      </c>
+      <c r="G342" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-07T02:20:26.164264</t>
+        </is>
+      </c>
+      <c r="H342" s="7" t="inlineStr">
+        <is>
+          <t>➜ Apply</t>
+        </is>
+      </c>
+    </row>
+    <row r="343" ht="28" customHeight="1">
+      <c r="A343" s="8" t="inlineStr">
+        <is>
+          <t>Research Scientist Intern - Applied Perception Science - PhD</t>
+        </is>
+      </c>
+      <c r="B343" s="9" t="inlineStr">
+        <is>
+          <t>Meta</t>
+        </is>
+      </c>
+      <c r="C343" s="10" t="inlineStr">
+        <is>
+          <t>https://www.metacareers.com/jobs/25766888559672059</t>
+        </is>
+      </c>
+      <c r="D343" s="11" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="E343" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F343" s="9" t="inlineStr">
+        <is>
+          <t>Rejected: Found dealbreaker terms in JD (phd)</t>
+        </is>
+      </c>
+      <c r="G343" s="9" t="inlineStr">
+        <is>
+          <t>2026-03-07T02:20:26.164264</t>
+        </is>
+      </c>
+      <c r="H343" s="7" t="inlineStr">
+        <is>
+          <t>➜ Apply</t>
+        </is>
+      </c>
+    </row>
+    <row r="344" ht="28" customHeight="1">
+      <c r="A344" s="8" t="inlineStr">
+        <is>
+          <t>Research Scientist Intern PhD - Applied Research</t>
+        </is>
+      </c>
+      <c r="B344" s="9" t="inlineStr">
+        <is>
+          <t>Meta</t>
+        </is>
+      </c>
+      <c r="C344" s="10" t="inlineStr">
+        <is>
+          <t>https://www.metacareers.com/jobs/2633206137040139</t>
+        </is>
+      </c>
+      <c r="D344" s="11" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="E344" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F344" s="9" t="inlineStr">
+        <is>
+          <t>Rejected: Found dealbreaker terms in JD (ph.d)</t>
+        </is>
+      </c>
+      <c r="G344" s="9" t="inlineStr">
+        <is>
+          <t>2026-03-07T02:20:26.164264</t>
+        </is>
+      </c>
+      <c r="H344" s="7" t="inlineStr">
+        <is>
+          <t>➜ Apply</t>
+        </is>
+      </c>
+    </row>
+    <row r="345" ht="28" customHeight="1">
+      <c r="A345" s="8" t="inlineStr">
+        <is>
+          <t>Research Scientist Intern - AI/ML - Core Ads Growth</t>
+        </is>
+      </c>
+      <c r="B345" s="9" t="inlineStr">
+        <is>
+          <t>Meta</t>
+        </is>
+      </c>
+      <c r="C345" s="10" t="inlineStr">
+        <is>
+          <t>https://www.metacareers.com/jobs/771948392580541</t>
+        </is>
+      </c>
+      <c r="D345" s="11" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="E345" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F345" s="9" t="inlineStr">
+        <is>
+          <t>Rejected: Non-US Location (London, UK)</t>
+        </is>
+      </c>
+      <c r="G345" s="9" t="inlineStr">
+        <is>
+          <t>2026-03-07T02:20:26.164264</t>
+        </is>
+      </c>
+      <c r="H345" s="7" t="inlineStr">
+        <is>
+          <t>➜ Apply</t>
+        </is>
+      </c>
+    </row>
+    <row r="346" ht="28" customHeight="1">
+      <c r="A346" s="8" t="inlineStr">
+        <is>
+          <t>ASA AI Exploration Team – Research Scientist Intern</t>
+        </is>
+      </c>
+      <c r="B346" s="9" t="inlineStr">
+        <is>
+          <t>Meta</t>
+        </is>
+      </c>
+      <c r="C346" s="10" t="inlineStr">
+        <is>
+          <t>https://www.metacareers.com/jobs/987681160814077</t>
+        </is>
+      </c>
+      <c r="D346" s="11" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="E346" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F346" s="9" t="inlineStr">
+        <is>
+          <t>Rejected: Found dealbreaker terms in JD (ph.d)</t>
+        </is>
+      </c>
+      <c r="G346" s="9" t="inlineStr">
+        <is>
+          <t>2026-03-07T02:20:26.164264</t>
+        </is>
+      </c>
+      <c r="H346" s="7" t="inlineStr">
+        <is>
+          <t>➜ Apply</t>
+        </is>
+      </c>
+    </row>
+    <row r="347" ht="28" customHeight="1">
+      <c r="A347" s="8" t="inlineStr">
+        <is>
+          <t>Customer Applications Engineer</t>
+        </is>
+      </c>
+      <c r="B347" s="9" t="inlineStr">
+        <is>
+          <t>Nokia</t>
+        </is>
+      </c>
+      <c r="C347" s="10" t="inlineStr">
+        <is>
+          <t>https://fa-evmr-saasfaprod1.fa.ocs.oraclecloud.com/hcmUI/...</t>
+        </is>
+      </c>
+      <c r="D347" s="11" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="E347" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F347" s="9" t="inlineStr">
+        <is>
+          <t>Rejected: Non-US Location (Ottawa, ON, Canada)</t>
+        </is>
+      </c>
+      <c r="G347" s="9" t="inlineStr">
+        <is>
+          <t>2026-03-07T02:20:26.164264</t>
+        </is>
+      </c>
+      <c r="H347" s="7" t="inlineStr">
+        <is>
+          <t>➜ Apply</t>
+        </is>
+      </c>
+    </row>
+    <row r="348" ht="28" customHeight="1">
+      <c r="A348" s="8" t="inlineStr">
+        <is>
+          <t>Research Scientist Intern - Multimodal Foundations - PhD</t>
+        </is>
+      </c>
+      <c r="B348" s="9" t="inlineStr">
+        <is>
+          <t>Meta</t>
+        </is>
+      </c>
+      <c r="C348" s="10" t="inlineStr">
+        <is>
+          <t>https://www.metacareers.com/jobs/898451286162557</t>
+        </is>
+      </c>
+      <c r="D348" s="11" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="E348" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F348" s="9" t="inlineStr">
+        <is>
+          <t>Rejected: Found dealbreaker terms in JD (phd)</t>
+        </is>
+      </c>
+      <c r="G348" s="9" t="inlineStr">
+        <is>
+          <t>2026-03-07T02:20:26.164264</t>
+        </is>
+      </c>
+      <c r="H348" s="7" t="inlineStr">
+        <is>
+          <t>➜ Apply</t>
+        </is>
+      </c>
+    </row>
+    <row r="349" ht="28" customHeight="1">
+      <c r="A349" s="8" t="inlineStr">
+        <is>
+          <t>Research Scientist Intern - Applied Vision and Image Quality - PhD</t>
+        </is>
+      </c>
+      <c r="B349" s="9" t="inlineStr">
+        <is>
+          <t>Meta</t>
+        </is>
+      </c>
+      <c r="C349" s="10" t="inlineStr">
+        <is>
+          <t>https://www.metacareers.com/jobs/1422892385992613</t>
+        </is>
+      </c>
+      <c r="D349" s="11" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="E349" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F349" s="9" t="inlineStr">
+        <is>
+          <t>Rejected: Found dealbreaker terms in JD (phd)</t>
+        </is>
+      </c>
+      <c r="G349" s="9" t="inlineStr">
+        <is>
+          <t>2026-03-07T02:20:26.164264</t>
+        </is>
+      </c>
+      <c r="H349" s="7" t="inlineStr">
+        <is>
+          <t>➜ Apply</t>
+        </is>
+      </c>
+    </row>
+    <row r="350" ht="28" customHeight="1">
+      <c r="A350" s="8" t="inlineStr">
+        <is>
+          <t>Research Scientist Intern - Mathematics - PhD</t>
+        </is>
+      </c>
+      <c r="B350" s="9" t="inlineStr">
+        <is>
+          <t>Meta</t>
+        </is>
+      </c>
+      <c r="C350" s="10" t="inlineStr">
+        <is>
+          <t>https://www.metacareers.com/jobs/1471311707754788</t>
+        </is>
+      </c>
+      <c r="D350" s="11" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="E350" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F350" s="9" t="inlineStr">
+        <is>
+          <t>Rejected: Found dealbreaker terms in JD (phd)</t>
+        </is>
+      </c>
+      <c r="G350" s="9" t="inlineStr">
+        <is>
+          <t>2026-03-07T02:20:26.164264</t>
+        </is>
+      </c>
+      <c r="H350" s="7" t="inlineStr">
+        <is>
+          <t>➜ Apply</t>
+        </is>
+      </c>
+    </row>
+    <row r="351" ht="28" customHeight="1">
+      <c r="A351" s="8" t="inlineStr">
+        <is>
+          <t>AI Research Assistant - PhD</t>
+        </is>
+      </c>
+      <c r="B351" s="9" t="inlineStr">
+        <is>
+          <t>Meta</t>
+        </is>
+      </c>
+      <c r="C351" s="10" t="inlineStr">
+        <is>
+          <t>https://www.metacareers.com/jobs/3250422131797159</t>
+        </is>
+      </c>
+      <c r="D351" s="11" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="E351" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F351" s="9" t="inlineStr">
+        <is>
+          <t>Rejected: Non-US Location (London, UK)</t>
+        </is>
+      </c>
+      <c r="G351" s="9" t="inlineStr">
+        <is>
+          <t>2026-03-07T02:20:26.164264</t>
+        </is>
+      </c>
+      <c r="H351" s="7" t="inlineStr">
+        <is>
+          <t>➜ Apply</t>
+        </is>
+      </c>
+    </row>
+    <row r="352" ht="28" customHeight="1">
+      <c r="A352" s="8" t="inlineStr">
+        <is>
+          <t>Machine Learning Intern</t>
+        </is>
+      </c>
+      <c r="B352" s="9" t="inlineStr">
+        <is>
+          <t>Deliveroo</t>
+        </is>
+      </c>
+      <c r="C352" s="10" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/deliveroo/09e09801-1f6b-4281-968...</t>
+        </is>
+      </c>
+      <c r="D352" s="11" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="E352" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F352" s="9" t="inlineStr">
+        <is>
+          <t>Rejected: Non-US Location (London, UK)</t>
+        </is>
+      </c>
+      <c r="G352" s="9" t="inlineStr">
+        <is>
+          <t>2026-03-07T02:20:26.164264</t>
+        </is>
+      </c>
+      <c r="H352" s="7" t="inlineStr">
+        <is>
+          <t>➜ Apply</t>
+        </is>
+      </c>
+    </row>
+    <row r="353" ht="28" customHeight="1">
+      <c r="A353" s="8" t="inlineStr">
+        <is>
+          <t>Research Scientist Intern - Language and Multimodal Research - PhD</t>
+        </is>
+      </c>
+      <c r="B353" s="9" t="inlineStr">
+        <is>
+          <t>Meta</t>
+        </is>
+      </c>
+      <c r="C353" s="10" t="inlineStr">
+        <is>
+          <t>https://www.metacareers.com/jobs/853054523849795</t>
+        </is>
+      </c>
+      <c r="D353" s="11" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="E353" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F353" s="9" t="inlineStr">
+        <is>
+          <t>Rejected: Found dealbreaker terms in JD (ph.d)</t>
+        </is>
+      </c>
+      <c r="G353" s="9" t="inlineStr">
+        <is>
+          <t>2026-03-07T02:20:26.164264</t>
+        </is>
+      </c>
+      <c r="H353" s="7" t="inlineStr">
+        <is>
+          <t>➜ Apply</t>
+        </is>
+      </c>
+    </row>
+    <row r="354" ht="28" customHeight="1">
+      <c r="A354" s="8" t="inlineStr">
+        <is>
+          <t>6G Intern Engineer</t>
+        </is>
+      </c>
+      <c r="B354" s="9" t="inlineStr">
+        <is>
+          <t>Nokia</t>
+        </is>
+      </c>
+      <c r="C354" s="10" t="inlineStr">
+        <is>
+          <t>https://fa-evmr-saasfaprod1.fa.ocs.oraclecloud.com/hcmUI/...</t>
+        </is>
+      </c>
+      <c r="D354" s="11" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="E354" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F354" s="9" t="inlineStr">
+        <is>
+          <t>Rejected: Non-US Location (United Kingdom)</t>
+        </is>
+      </c>
+      <c r="G354" s="9" t="inlineStr">
+        <is>
+          <t>2026-03-07T02:20:26.164264</t>
+        </is>
+      </c>
+      <c r="H354" s="7" t="inlineStr">
+        <is>
+          <t>➜ Apply</t>
+        </is>
+      </c>
+    </row>
+    <row r="355" ht="28" customHeight="1">
+      <c r="A355" s="3" t="inlineStr">
+        <is>
+          <t>Services AI and Automation Intern/Co-op</t>
+        </is>
+      </c>
+      <c r="B355" s="4" t="inlineStr">
+        <is>
+          <t>Nokia</t>
+        </is>
+      </c>
+      <c r="C355" s="5" t="inlineStr">
+        <is>
+          <t>https://fa-evmr-saasfaprod1.fa.ocs.oraclecloud.com/hcmUI/...</t>
+        </is>
+      </c>
+      <c r="D355" s="6" t="inlineStr">
+        <is>
+          <t>shortlisted</t>
+        </is>
+      </c>
+      <c r="E355" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="F355" s="4" t="inlineStr">
+        <is>
+          <t>The job does not explicitly require US Citizenship or Security Clearance, so no auto-reject. The job requires 4 months of experience, which is less than 3 years, so no deduction for experience gap. The job does not list any core technologies that the candidate is missing, so no deduction for core tech stack mismatch. The job is in the Services AI and Automation domain, which is relevant to the candidate's interests, so no domain penalty. The role title 'Services AI and Automation Intern/Co-op' matches one of the candidate's target roles, so a +1 is added. The candidate's score is 6, which meets the score threshold.</t>
+        </is>
+      </c>
+      <c r="G355" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-07T02:20:26.164264</t>
+        </is>
+      </c>
+      <c r="H355" s="7" t="inlineStr">
+        <is>
+          <t>➜ Apply</t>
+        </is>
+      </c>
+    </row>
+    <row r="356" ht="28" customHeight="1">
+      <c r="A356" s="3" t="inlineStr">
+        <is>
+          <t>Editorial AI Development Intern</t>
+        </is>
+      </c>
+      <c r="B356" s="4" t="inlineStr">
+        <is>
+          <t>Hearst</t>
+        </is>
+      </c>
+      <c r="C356" s="5" t="inlineStr">
+        <is>
+          <t>https://eevd.fa.us6.oraclecloud.com/hcmUI/CandidateExperi...</t>
+        </is>
+      </c>
+      <c r="D356" s="6" t="inlineStr">
+        <is>
+          <t>shortlisted</t>
+        </is>
+      </c>
+      <c r="E356" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="F356" s="4" t="inlineStr">
+        <is>
+          <t>The job is explicitly for an Editorial AI Development Intern, which is an internship role, so no auto-reject occurs. The job does not require 3-4 years of experience, so no experience gap deduction. The job does not list any specific core tech stack requirements, so no core tech stack mismatch deduction. The job is in the news and journalism domain, which is not a non-tech company, so no domain penalty. The role title does not exactly match the candidate's target roles, so no role relevance bonus. The candidate is enrolled in a Master of Computer Science and has relevant skills, but the job requires specific experience in Python APIs and prompt design, which the candidate does not have. The candidate is not a current Stanford University student, so they are not eligible for the internship. The candidate's visa status is not relevant as the job does not require US citizenship or security clearance.</t>
+        </is>
+      </c>
+      <c r="G356" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-07T02:20:26.164264</t>
+        </is>
+      </c>
+      <c r="H356" s="7" t="inlineStr">
+        <is>
+          <t>➜ Apply</t>
+        </is>
+      </c>
+    </row>
+    <row r="357" ht="28" customHeight="1">
+      <c r="A357" s="3" t="inlineStr">
+        <is>
+          <t>Support Group Intern - Data Engineering</t>
+        </is>
+      </c>
+      <c r="B357" s="4" t="inlineStr">
+        <is>
+          <t>Sundt</t>
+        </is>
+      </c>
+      <c r="C357" s="5" t="inlineStr">
+        <is>
+          <t>https://eewl.fa.us6.oraclecloud.com/hcmUI/CandidateExperi...</t>
+        </is>
+      </c>
+      <c r="D357" s="6" t="inlineStr">
+        <is>
+          <t>shortlisted</t>
+        </is>
+      </c>
+      <c r="E357" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="F357" s="4" t="inlineStr">
+        <is>
+          <t>The job is explicitly for a Data Engineering Intern, which matches the candidate's target roles. The job does not require US Citizenship or Security Clearance. The job does not explicitly require 5+ years of experience. The job requires experience with at least one programming language (SQL, Python, or similar), which the candidate has. The job is not in a non-tech company or in a domain that would incur a penalty. The candidate's experience level is a current university student, which matches the job requirement. The job does not require 5+ years of experience, so no auto-reject applies. The candidate has experience with SQL, which is a required technology, and no other core techs are missing. The job is not in a domain that incurs a penalty. The role title matches the candidate's target roles, so a bonus is added.</t>
+        </is>
+      </c>
+      <c r="G357" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-07T02:20:26.164264</t>
+        </is>
+      </c>
+      <c r="H357" s="7" t="inlineStr">
+        <is>
+          <t>➜ Apply</t>
+        </is>
+      </c>
+    </row>
+    <row r="358" ht="28" customHeight="1">
+      <c r="A358" s="8" t="inlineStr">
+        <is>
+          <t>Intern Engineer</t>
+        </is>
+      </c>
+      <c r="B358" s="9" t="inlineStr">
+        <is>
+          <t>General Dynamics Mission Systems</t>
+        </is>
+      </c>
+      <c r="C358" s="10" t="inlineStr">
+        <is>
+          <t>https://careers-gdms.icims.com/jobs/71285/job?mobile=true...</t>
+        </is>
+      </c>
+      <c r="D358" s="11" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="E358" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F358" s="9" t="inlineStr">
+        <is>
+          <t>Rejected: Found dealbreaker terms in JD (clearance)</t>
+        </is>
+      </c>
+      <c r="G358" s="9" t="inlineStr">
+        <is>
+          <t>2026-03-07T02:20:26.164264</t>
+        </is>
+      </c>
+      <c r="H358" s="7" t="inlineStr">
+        <is>
+          <t>➜ Apply</t>
+        </is>
+      </c>
+    </row>
+    <row r="359" ht="28" customHeight="1">
+      <c r="A359" s="3" t="inlineStr">
+        <is>
+          <t>Data Analyst Intern</t>
+        </is>
+      </c>
+      <c r="B359" s="4" t="inlineStr">
+        <is>
+          <t>Argonne National Laboratory</t>
+        </is>
+      </c>
+      <c r="C359" s="5" t="inlineStr">
+        <is>
+          <t>https://argonne.wd1.myworkdayjobs.com/EDU_PUB/job/Lemont-...</t>
+        </is>
+      </c>
+      <c r="D359" s="6" t="inlineStr">
+        <is>
+          <t>shortlisted</t>
+        </is>
+      </c>
+      <c r="E359" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="F359" s="4" t="inlineStr">
+        <is>
+          <t>The job title is 'Data Analyst Intern', which is an internship role. The candidate is targeting internship roles, so there is no experience gap. The job does not explicitly require US citizenship or a security clearance. The candidate's skills and experience align well with the job requirements, but the job does not mention any specific core technologies that the candidate is missing. The domain is not in finance, banking, or non-tech sectors, so there is no domain penalty. The candidate's target roles include 'Data Scientist Intern', which is relevant to the job, but the job title is 'Data Analyst Intern', so there is a slight mismatch. The candidate's visa status is not a factor since the job does not require US citizenship.</t>
+        </is>
+      </c>
+      <c r="G359" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-07T02:20:26.164264</t>
+        </is>
+      </c>
+      <c r="H359" s="7" t="inlineStr">
+        <is>
+          <t>➜ Apply</t>
+        </is>
+      </c>
+    </row>
+    <row r="360" ht="28" customHeight="1">
+      <c r="A360" s="3" t="inlineStr">
+        <is>
+          <t>Intern Design Engineer</t>
+        </is>
+      </c>
+      <c r="B360" s="4" t="inlineStr">
+        <is>
+          <t>Micron Technology</t>
+        </is>
+      </c>
+      <c r="C360" s="5" t="inlineStr">
+        <is>
+          <t>https://micron.wd1.myworkdayjobs.com/External/job/San-Jos...</t>
+        </is>
+      </c>
+      <c r="D360" s="6" t="inlineStr">
+        <is>
+          <t>shortlisted</t>
+        </is>
+      </c>
+      <c r="E360" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="F360" s="4" t="inlineStr">
+        <is>
+          <t>The job title 'Intern Design Engineer' does not explicitly require US Citizenship or Security Clearance, so no auto-reject occurs. The job does not specify a required experience level, so no experience gap deduction applies. There are no core tech stack mismatches as the candidate has a broad range of relevant skills. The job is in the tech domain, so no domain penalty applies. The role title does not exactly match the candidate's target roles, but it is in a tech-related field, so no role relevance bonus is added. The candidate's visa status is a concern, but it does not directly affect the score calculation.</t>
+        </is>
+      </c>
+      <c r="G360" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-07T02:20:26.164264</t>
+        </is>
+      </c>
+      <c r="H360" s="7" t="inlineStr">
+        <is>
+          <t>➜ Apply</t>
+        </is>
+      </c>
+    </row>
+    <row r="361" ht="28" customHeight="1">
+      <c r="A361" s="8" t="inlineStr">
+        <is>
+          <t>Backend Engineer Intern</t>
+        </is>
+      </c>
+      <c r="B361" s="9" t="inlineStr">
+        <is>
+          <t>Proofpoint</t>
+        </is>
+      </c>
+      <c r="C361" s="10" t="inlineStr">
+        <is>
+          <t>https://proofpoint.wd5.myworkdayjobs.com/proofpointcareer...</t>
+        </is>
+      </c>
+      <c r="D361" s="11" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="E361" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F361" s="9" t="inlineStr">
+        <is>
+          <t>Rejected: Non-US Location (Belfast, UK)</t>
+        </is>
+      </c>
+      <c r="G361" s="9" t="inlineStr">
+        <is>
+          <t>2026-03-07T02:20:26.164264</t>
+        </is>
+      </c>
+      <c r="H361" s="7" t="inlineStr">
+        <is>
+          <t>➜ Apply</t>
+        </is>
+      </c>
+    </row>
+    <row r="362" ht="28" customHeight="1">
+      <c r="A362" s="3" t="inlineStr">
+        <is>
+          <t>Data Science Intern</t>
+        </is>
+      </c>
+      <c r="B362" s="4" t="inlineStr">
+        <is>
+          <t>BorgWarner</t>
+        </is>
+      </c>
+      <c r="C362" s="5" t="inlineStr">
+        <is>
+          <t>https://borgwarner.wd5.myworkdayjobs.com/BorgWarner_Caree...</t>
+        </is>
+      </c>
+      <c r="D362" s="6" t="inlineStr">
+        <is>
+          <t>shortlisted</t>
+        </is>
+      </c>
+      <c r="E362" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="F362" s="4" t="inlineStr">
+        <is>
+          <t>The job is for a Data Science Intern, which is an internship role, so no experience gap deduction applies. The candidate's skills and experience align well with the job requirements, including knowledge of Python, machine learning, and data science tools. The candidate's current enrollment status and need for sponsorship do not affect the score as the job does not explicitly require US citizenship or a security clearance. The job is not in a non-tech domain, so no domain penalty applies. The role title does not exactly match the candidate's target roles, but it is relevant to their interests, so no role relevance bonus is added.</t>
+        </is>
+      </c>
+      <c r="G362" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-07T02:20:26.164264</t>
+        </is>
+      </c>
+      <c r="H362" s="7" t="inlineStr">
+        <is>
+          <t>➜ Apply</t>
+        </is>
+      </c>
+    </row>
+    <row r="363" ht="28" customHeight="1">
+      <c r="A363" s="3" t="inlineStr">
+        <is>
+          <t>Atlas VLA Research Intern</t>
+        </is>
+      </c>
+      <c r="B363" s="4" t="inlineStr">
+        <is>
+          <t>Boston Dynamics</t>
+        </is>
+      </c>
+      <c r="C363" s="5" t="inlineStr">
+        <is>
+          <t>https://bostondynamics.wd1.myworkdayjobs.com/Boston_Dynam...</t>
+        </is>
+      </c>
+      <c r="D363" s="6" t="inlineStr">
+        <is>
+          <t>shortlisted</t>
+        </is>
+      </c>
+      <c r="E363" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="F363" s="4" t="inlineStr">
+        <is>
+          <t>The job does not explicitly require US Citizenship or Security Clearance, so no auto-reject occurs. The job is for an intern, so no experience gap deduction applies. The job does not mention any specific core tech stack that the candidate is missing, so no core tech stack mismatch deduction applies. The domain is not finance, banking, or non-tech, so no domain penalty applies. The role title does not exactly match the candidate's target roles, so no role relevance bonus applies. The candidate is an intern and does not require 5+ years of experience, so the score remains 10.</t>
+        </is>
+      </c>
+      <c r="G363" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-07T02:20:26.164264</t>
+        </is>
+      </c>
+      <c r="H363" s="7" t="inlineStr">
+        <is>
+          <t>➜ Apply</t>
+        </is>
+      </c>
+    </row>
+    <row r="364" ht="28" customHeight="1">
+      <c r="A364" s="8" t="inlineStr">
+        <is>
+          <t>Intern - On Device Physical AI</t>
+        </is>
+      </c>
+      <c r="B364" s="9" t="inlineStr">
+        <is>
+          <t>Samsung Research America</t>
+        </is>
+      </c>
+      <c r="C364" s="10" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/samsungresearchamericain...</t>
+        </is>
+      </c>
+      <c r="D364" s="11" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="E364" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F364" s="9" t="inlineStr">
+        <is>
+          <t>Rejected: Found dealbreaker terms in JD (ph.d)</t>
+        </is>
+      </c>
+      <c r="G364" s="9" t="inlineStr">
+        <is>
+          <t>2026-03-07T02:20:26.164264</t>
+        </is>
+      </c>
+      <c r="H364" s="7" t="inlineStr">
+        <is>
+          <t>➜ Apply</t>
+        </is>
+      </c>
+    </row>
+    <row r="365" ht="28" customHeight="1">
+      <c r="A365" s="3" t="inlineStr">
+        <is>
+          <t>Intern Software Engineer</t>
+        </is>
+      </c>
+      <c r="B365" s="4" t="inlineStr">
+        <is>
+          <t>Zeiss</t>
+        </is>
+      </c>
+      <c r="C365" s="5" t="inlineStr">
+        <is>
+          <t>https://zeissgroup.wd3.myworkdayjobs.com/External/job/Dub...</t>
+        </is>
+      </c>
+      <c r="D365" s="6" t="inlineStr">
+        <is>
+          <t>shortlisted</t>
+        </is>
+      </c>
+      <c r="E365" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="F365" s="4" t="inlineStr">
+        <is>
+          <t>The job is an Intern Software Engineer position, which does not auto-reject the candidate based on experience. The candidate has relevant skills in Full Stack Development, AI/ML, and distributed systems, which aligns well with the job requirements. The candidate's experience level is consistent with an intern, and the job does not explicitly require US Citizenship or Security Clearance. The job does not mention any specific core technologies that the candidate is missing, and it is not in a domain that incurs a penalty. The role title does not exactly match the candidate's target roles, but it is close enough to not warrant a significant bonus.</t>
+        </is>
+      </c>
+      <c r="G365" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-07T02:20:26.164264</t>
+        </is>
+      </c>
+      <c r="H365" s="7" t="inlineStr">
+        <is>
+          <t>➜ Apply</t>
+        </is>
+      </c>
+    </row>
+    <row r="366" ht="28" customHeight="1">
+      <c r="A366" s="3" t="inlineStr">
+        <is>
+          <t>Data Analyst Intern – Path to Full-Time</t>
+        </is>
+      </c>
+      <c r="B366" s="4" t="inlineStr">
+        <is>
+          <t>Johnson Brothers Liquor Company</t>
+        </is>
+      </c>
+      <c r="C366" s="5" t="inlineStr">
+        <is>
+          <t>https://johnsonbrothers.wd5.myworkdayjobs.com/johnsonbrot...</t>
+        </is>
+      </c>
+      <c r="D366" s="6" t="inlineStr">
+        <is>
+          <t>shortlisted</t>
+        </is>
+      </c>
+      <c r="E366" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="F366" s="4" t="inlineStr">
+        <is>
+          <t>The job is explicitly for a Data Analyst Intern, which is not a role that matches the candidate's target roles. The job does not require 5+ years of experience, so no deductions are applied for experience gap. There are no core tech stack mismatches as the job description does not specify any required technologies. The domain is non-tech, which applies a -3 penalty. The candidate is an intern, so no additional penalties apply. The candidate's visa status is not relevant to this job.</t>
+        </is>
+      </c>
+      <c r="G366" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-07T02:20:26.164264</t>
+        </is>
+      </c>
+      <c r="H366" s="7" t="inlineStr">
+        <is>
+          <t>➜ Apply</t>
+        </is>
+      </c>
+    </row>
+    <row r="367" ht="28" customHeight="1">
+      <c r="A367" s="3" t="inlineStr">
+        <is>
+          <t>GE Vernova Time-Series Foundation Models Research Intern</t>
+        </is>
+      </c>
+      <c r="B367" s="4" t="inlineStr">
+        <is>
+          <t>GE Vernova</t>
+        </is>
+      </c>
+      <c r="C367" s="5" t="inlineStr">
+        <is>
+          <t>https://gevernova.wd5.myworkdayjobs.com/only_confidential...</t>
+        </is>
+      </c>
+      <c r="D367" s="6" t="inlineStr">
+        <is>
+          <t>shortlisted</t>
+        </is>
+      </c>
+      <c r="E367" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="F367" s="4" t="inlineStr">
+        <is>
+          <t>The job does not explicitly require US Citizenship or Security Clearance, so no auto-reject. The job title 'GE Vernova Time-Series Foundation Models Research Intern' does not explicitly state a senior or staff level, so no auto-reject. The job requires 3-4 years of experience, which deducts -2. The job is in the AI/ML domain, so no domain penalty. The role title 'Research Intern' does not exactly match the candidate's target roles, so no role relevance bonus. The candidate's experience and skills align well with the job requirements, but the job title does not exactly match the candidate's target roles, hence no role relevance bonus.</t>
+        </is>
+      </c>
+      <c r="G367" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-07T02:20:26.164264</t>
+        </is>
+      </c>
+      <c r="H367" s="7" t="inlineStr">
+        <is>
+          <t>➜ Apply</t>
+        </is>
+      </c>
+    </row>
+    <row r="368" ht="28" customHeight="1">
+      <c r="A368" s="8" t="inlineStr">
+        <is>
+          <t>Machine Learning Research Intern</t>
+        </is>
+      </c>
+      <c r="B368" s="9" t="inlineStr">
+        <is>
+          <t>Profluent</t>
+        </is>
+      </c>
+      <c r="C368" s="10" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/profluent/jobs/4563429008</t>
+        </is>
+      </c>
+      <c r="D368" s="11" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="E368" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F368" s="9" t="inlineStr">
+        <is>
+          <t>Rejected: Found dealbreaker terms in JD (phd)</t>
+        </is>
+      </c>
+      <c r="G368" s="9" t="inlineStr">
+        <is>
+          <t>2026-03-07T02:20:26.164264</t>
+        </is>
+      </c>
+      <c r="H368" s="7" t="inlineStr">
+        <is>
+          <t>➜ Apply</t>
+        </is>
+      </c>
+    </row>
+    <row r="369" ht="28" customHeight="1">
+      <c r="A369" s="8" t="inlineStr">
+        <is>
+          <t>Foundation Models for Autonomous Driving AI Engineering Intern</t>
+        </is>
+      </c>
+      <c r="B369" s="9" t="inlineStr">
+        <is>
+          <t>Robert Bosch Venture Capital</t>
+        </is>
+      </c>
+      <c r="C369" s="10" t="inlineStr">
+        <is>
+          <t>https://jobs.smartrecruiters.com/BoschGroup/744000112999098</t>
+        </is>
+      </c>
+      <c r="D369" s="11" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="E369" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F369" s="9" t="inlineStr">
+        <is>
+          <t>Rejected: Found dealbreaker terms in JD (phd)</t>
+        </is>
+      </c>
+      <c r="G369" s="9" t="inlineStr">
+        <is>
+          <t>2026-03-07T02:20:26.164264</t>
+        </is>
+      </c>
+      <c r="H369" s="7" t="inlineStr">
+        <is>
+          <t>➜ Apply</t>
+        </is>
+      </c>
+    </row>
+    <row r="370" ht="28" customHeight="1">
+      <c r="A370" s="3" t="inlineStr">
+        <is>
+          <t>Data Solutions</t>
+        </is>
+      </c>
+      <c r="B370" s="4" t="inlineStr">
+        <is>
+          <t>AcreTrader</t>
+        </is>
+      </c>
+      <c r="C370" s="5" t="inlineStr">
+        <is>
+          <t>https://ats.rippling.com/acretrader-jobs/jobs/51cfccd9-33...</t>
+        </is>
+      </c>
+      <c r="D370" s="6" t="inlineStr">
+        <is>
+          <t>shortlisted</t>
+        </is>
+      </c>
+      <c r="E370" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="F370" s="4" t="inlineStr">
+        <is>
+          <t>The job is explicitly for an intern position, which does not require any experience. The candidate is enrolled in a Master's program, which aligns with the educational requirement. The job does not explicitly require US citizenship or a security clearance. The role is not senior or staff level. The core tech stack mismatch is not applicable as there are no specific core technologies mentioned as required. The domain is not in finance, banking, or non-tech sectors. The role title does not match the candidate's target roles exactly, but it is close enough to not significantly impact the score.</t>
+        </is>
+      </c>
+      <c r="G370" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-07T02:20:26.164264</t>
+        </is>
+      </c>
+      <c r="H370" s="7" t="inlineStr">
+        <is>
+          <t>➜ Apply</t>
+        </is>
+      </c>
+    </row>
+    <row r="371" ht="28" customHeight="1">
+      <c r="A371" s="3" t="inlineStr">
+        <is>
+          <t>Data Analytics Intern - Summer 2026</t>
+        </is>
+      </c>
+      <c r="B371" s="4" t="inlineStr">
+        <is>
+          <t>Cloudflare</t>
+        </is>
+      </c>
+      <c r="C371" s="5" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/cloudflare/jobs/7668989</t>
+        </is>
+      </c>
+      <c r="D371" s="6" t="inlineStr">
+        <is>
+          <t>shortlisted</t>
+        </is>
+      </c>
+      <c r="E371" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="F371" s="4" t="inlineStr">
+        <is>
+          <t>The job is for a Data Analytics Intern, which is an internship role, so no experience gap deduction applies. The candidate is currently enrolled in a Master's degree, which aligns with the required educational background. The candidate has relevant skills in data analysis, SQL, and data visualization, which are required for the role. The job does not explicitly require US citizenship or a security clearance, and it is an internship, so no auto-rejects apply. The job does not require 5+ years of experience, so no experience gap deduction applies. The domain is in data analytics, which is not a domain penalty. The role title matches the candidate's target roles, so a role relevance bonus is applied. The candidate's skills and experience are well-aligned with the job requirements, and the score is above the threshold of 6.</t>
+        </is>
+      </c>
+      <c r="G371" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-07T02:20:26.164264</t>
+        </is>
+      </c>
+      <c r="H371" s="7" t="inlineStr">
+        <is>
+          <t>➜ Apply</t>
+        </is>
+      </c>
+    </row>
+    <row r="372" ht="28" customHeight="1">
+      <c r="A372" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineer Intern/Co-op</t>
+        </is>
+      </c>
+      <c r="B372" s="4" t="inlineStr">
+        <is>
+          <t>KION Group</t>
+        </is>
+      </c>
+      <c r="C372" s="5" t="inlineStr">
+        <is>
+          <t>https://kiongroup.wd3.myworkdayjobs.com/kiongroup/job/Gra...</t>
+        </is>
+      </c>
+      <c r="D372" s="6" t="inlineStr">
+        <is>
+          <t>shortlisted</t>
+        </is>
+      </c>
+      <c r="E372" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="F372" s="4" t="inlineStr">
+        <is>
+          <t>Auto-Shortlisted (Protected Title)</t>
+        </is>
+      </c>
+      <c r="G372" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-07T02:20:26.164264</t>
+        </is>
+      </c>
+      <c r="H372" s="7" t="inlineStr">
+        <is>
+          <t>➜ Apply</t>
+        </is>
+      </c>
+    </row>
+    <row r="373" ht="28" customHeight="1">
+      <c r="A373" s="3" t="inlineStr">
+        <is>
+          <t>Part Time Student - Software Engineer</t>
+        </is>
+      </c>
+      <c r="B373" s="4" t="inlineStr">
+        <is>
+          <t>John Deere</t>
+        </is>
+      </c>
+      <c r="C373" s="5" t="inlineStr">
+        <is>
+          <t>https://johndeere.eightfold.ai/careers/job/137479561561</t>
+        </is>
+      </c>
+      <c r="D373" s="6" t="inlineStr">
+        <is>
+          <t>shortlisted</t>
+        </is>
+      </c>
+      <c r="E373" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="F373" s="4" t="inlineStr">
+        <is>
+          <t>The job is for a Part Time Student - Software Engineer, which is an internship. The candidate is currently enrolled in a Master of Computer Science program, making them a strong fit for the role. The job does not explicitly require US Citizenship or a Security Clearance, so no auto-reject applies. The job does not specify a required number of years of experience, so no experience gap deduction applies. The core tech stack required includes React, Node.js, Python, and SQL, which the candidate has experience with. The job is in the technology domain, so no domain penalty applies. The role title matches the candidate's target roles exactly, so a +1 bonus is applied. The candidate's score is 8, which meets the score threshold of 6.</t>
+        </is>
+      </c>
+      <c r="G373" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-07T02:20:26.164264</t>
+        </is>
+      </c>
+      <c r="H373" s="7" t="inlineStr">
+        <is>
+          <t>➜ Apply</t>
+        </is>
+      </c>
+    </row>
+    <row r="374" ht="28" customHeight="1">
+      <c r="A374" s="3" t="inlineStr">
+        <is>
+          <t>Data Science Intern</t>
+        </is>
+      </c>
+      <c r="B374" s="4" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group</t>
+        </is>
+      </c>
+      <c r="C374" s="5" t="inlineStr">
+        <is>
+          <t>https://aaaie.wd1.myworkdayjobs.com/CSAACareers2/job/Neva...</t>
+        </is>
+      </c>
+      <c r="D374" s="6" t="inlineStr">
+        <is>
+          <t>shortlisted</t>
+        </is>
+      </c>
+      <c r="E374" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="F374" s="4" t="inlineStr">
+        <is>
+          <t>The job is for a Data Science Intern, which is an internship role, so no experience gap deduction applies. The candidate has relevant skills in AI/ML and full stack development, but the job description does not explicitly mention any core technologies that the candidate is missing. The candidate's role title does not exactly match the job title, but it is close enough to not warrant a bonus. The job is not in a non-tech company or in a domain that would apply a penalty. The candidate requires sponsorship, which is not an auto-reject criterion. The candidate's score is 8, which meets the threshold of 6.</t>
+        </is>
+      </c>
+      <c r="G374" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-07T02:20:26.164264</t>
+        </is>
+      </c>
+      <c r="H374" s="7" t="inlineStr">
+        <is>
+          <t>➜ Apply</t>
+        </is>
+      </c>
+    </row>
+    <row r="375" ht="28" customHeight="1">
+      <c r="A375" s="3" t="inlineStr">
+        <is>
+          <t>Mobile Engineering Intern</t>
+        </is>
+      </c>
+      <c r="B375" s="4" t="inlineStr">
+        <is>
+          <t>Span</t>
+        </is>
+      </c>
+      <c r="C375" s="5" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/span/722b25c6-e62e-44d3-ad9b-b2e...</t>
+        </is>
+      </c>
+      <c r="D375" s="6" t="inlineStr">
+        <is>
+          <t>shortlisted</t>
+        </is>
+      </c>
+      <c r="E375" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="F375" s="4" t="inlineStr">
+        <is>
+          <t>The job is for a Mobile Engineering Intern, which is an internship role, so there is no experience gap. The candidate has relevant skills in Full Stack Development, AI Agents, LLM pipelines, Machine Learning, and Software Engineering, but the job does not explicitly require any of these specific technologies. The candidate is enrolled in a Master of Computer Science, which is relevant. The job does not explicitly require US Citizenship or Security Clearance, and it is an internship, so there is no domain penalty. The candidate is willing to relocate and does not require sponsorship, which aligns with the job requirements. The candidate's experience level is consistent with the internship role, and the job does not require 5+ years of experience. The candidate's role title does not exactly match the target roles, but it is close, so no bonus is added.</t>
+        </is>
+      </c>
+      <c r="G375" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-07T02:20:26.164264</t>
+        </is>
+      </c>
+      <c r="H375" s="7" t="inlineStr">
+        <is>
+          <t>➜ Apply</t>
+        </is>
+      </c>
+    </row>
+    <row r="376" ht="28" customHeight="1">
+      <c r="A376" s="3" t="inlineStr">
+        <is>
+          <t>Lab Systems Engineering Co-op</t>
+        </is>
+      </c>
+      <c r="B376" s="4" t="inlineStr">
+        <is>
+          <t>Vertex Pharmaceuticals</t>
+        </is>
+      </c>
+      <c r="C376" s="5" t="inlineStr">
+        <is>
+          <t>https://vrtx.wd501.myworkdayjobs.com/vertex_careers/job/B...</t>
+        </is>
+      </c>
+      <c r="D376" s="6" t="inlineStr">
+        <is>
+          <t>shortlisted</t>
+        </is>
+      </c>
+      <c r="E376" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="F376" s="4" t="inlineStr">
+        <is>
+          <t>The job does not explicitly require US Citizenship or a Security Clearance, so no auto-reject. The job is a co-op role, which is an internship, so no experience gap deduction. The job does not mention any specific core tech stack mismatch, so no deduction for that. The job is in the pharmaceutical industry, which is not a non-tech company, so no domain penalty. The role title does not exactly match the candidate's target roles, but it involves AI/ML work, so +1. The candidate is enrolled in an advanced degree program and is available to work full-time onsite, so no additional deductions. The candidate's score is 8, which is above the threshold of 6.</t>
+        </is>
+      </c>
+      <c r="G376" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-07T02:20:26.164264</t>
+        </is>
+      </c>
+      <c r="H376" s="7" t="inlineStr">
+        <is>
+          <t>➜ Apply</t>
+        </is>
+      </c>
+    </row>
+    <row r="377" ht="28" customHeight="1">
+      <c r="A377" s="8" t="inlineStr">
+        <is>
+          <t>AI &amp; Automation Student</t>
+        </is>
+      </c>
+      <c r="B377" s="9" t="inlineStr">
+        <is>
+          <t>AtkinsRéalis</t>
+        </is>
+      </c>
+      <c r="C377" s="10" t="inlineStr">
+        <is>
+          <t>https://slihrms.wd3.myworkdayjobs.com/careers/job/CAONMis...</t>
+        </is>
+      </c>
+      <c r="D377" s="11" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="E377" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F377" s="9" t="inlineStr">
+        <is>
+          <t>Rejected: Non-US Location (Mississauga, ON, Canada)</t>
+        </is>
+      </c>
+      <c r="G377" s="9" t="inlineStr">
+        <is>
+          <t>2026-03-07T02:20:26.164264</t>
+        </is>
+      </c>
+      <c r="H377" s="7" t="inlineStr">
+        <is>
+          <t>➜ Apply</t>
+        </is>
+      </c>
+    </row>
+    <row r="378" ht="28" customHeight="1">
+      <c r="A378" s="3" t="inlineStr">
+        <is>
+          <t>Data Science Intern</t>
+        </is>
+      </c>
+      <c r="B378" s="4" t="inlineStr">
+        <is>
+          <t>Jabil</t>
+        </is>
+      </c>
+      <c r="C378" s="5" t="inlineStr">
+        <is>
+          <t>https://jabil.wd5.myworkdayjobs.com/Jabil_Careers/job/Rem...</t>
+        </is>
+      </c>
+      <c r="D378" s="6" t="inlineStr">
+        <is>
+          <t>shortlisted</t>
+        </is>
+      </c>
+      <c r="E378" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="F378" s="4" t="inlineStr">
+        <is>
+          <t>The job is for a Data Science Intern, which is an internship role, so no experience gap deduction applies. The candidate has a Master of Computer Science degree, which is relevant, but the job does not explicitly require US Citizenship or Security Clearance. The candidate's skills and experience align well with the job requirements, particularly in AI/ML and data science. There are no core tech stack mismatches, and the domain is relevant to the candidate's interests. The candidate's preferences for internship roles and open location are also aligned with the job.</t>
+        </is>
+      </c>
+      <c r="G378" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-07T02:20:26.164264</t>
+        </is>
+      </c>
+      <c r="H378" s="7" t="inlineStr">
+        <is>
+          <t>➜ Apply</t>
+        </is>
+      </c>
+    </row>
+    <row r="379" ht="28" customHeight="1">
+      <c r="A379" s="3" t="inlineStr">
+        <is>
+          <t>Full Stack &amp; GenAI Engineer Intern</t>
+        </is>
+      </c>
+      <c r="B379" s="4" t="inlineStr">
+        <is>
+          <t>Skechers</t>
+        </is>
+      </c>
+      <c r="C379" s="5" t="inlineStr">
+        <is>
+          <t>https://skechers.wd5.myworkdayjobs.com/One-career-site/jo...</t>
+        </is>
+      </c>
+      <c r="D379" s="6" t="inlineStr">
+        <is>
+          <t>shortlisted</t>
+        </is>
+      </c>
+      <c r="E379" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="F379" s="4" t="inlineStr">
+        <is>
+          <t>The job is for a Full Stack &amp; GenAI Engineer Intern at Skechers, a retail company. The candidate is a Master's student with relevant skills in Full Stack Development, AI/ML, and GenAI. However, the job does not explicitly require US Citizenship or a Security Clearance, and it is an internship, so it does not auto-reject. The experience gap is not significant as the candidate has relevant experience. There is no core tech mismatch, and the domain is retail, which has a domain penalty of -3. The role title does not exactly match the candidate's target roles, but it involves AI/ML work, which adds a +1. The final score is 7, which meets the candidate's score threshold of 6.</t>
+        </is>
+      </c>
+      <c r="G379" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-07T02:20:26.164264</t>
+        </is>
+      </c>
+      <c r="H379" s="7" t="inlineStr">
+        <is>
+          <t>➜ Apply</t>
+        </is>
+      </c>
+    </row>
+    <row r="380" ht="28" customHeight="1">
+      <c r="A380" s="3" t="inlineStr">
+        <is>
+          <t>Sustainable Buildings &amp; AI Research Intern</t>
+        </is>
+      </c>
+      <c r="B380" s="4" t="inlineStr">
+        <is>
+          <t>Autodesk</t>
+        </is>
+      </c>
+      <c r="C380" s="5" t="inlineStr">
+        <is>
+          <t>https://autodesk.wd1.myworkdayjobs.com/uni/job/California...</t>
+        </is>
+      </c>
+      <c r="D380" s="6" t="inlineStr">
+        <is>
+          <t>shortlisted</t>
+        </is>
+      </c>
+      <c r="E380" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="F380" s="4" t="inlineStr">
+        <is>
+          <t>The job does not explicitly require US Citizenship or Security Clearance, so no auto-reject. The job is not a senior/managerial role, so no auto-reject. The job requires 3-4 years of experience, so -2. The job is in the Architecture, Engineering &amp; Construction domain, so no domain penalty. The role title does not match the candidate's target roles exactly, so no role relevance bonus. The candidate's skills and experience align well with the job requirements, but the job does not explicitly mention AI/ML work, so no role relevance bonus. The candidate's visa status is a preference, not a requirement, so no additional deductions. The score is 8 after applying all deductions.</t>
+        </is>
+      </c>
+      <c r="G380" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-07T02:20:26.164264</t>
+        </is>
+      </c>
+      <c r="H380" s="7" t="inlineStr">
+        <is>
+          <t>➜ Apply</t>
+        </is>
+      </c>
+    </row>
+    <row r="381" ht="28" customHeight="1">
+      <c r="A381" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineering Intern</t>
+        </is>
+      </c>
+      <c r="B381" s="4" t="inlineStr">
+        <is>
+          <t>Schweitzer Engineering Laboratories</t>
+        </is>
+      </c>
+      <c r="C381" s="5" t="inlineStr">
+        <is>
+          <t>https://selinc.wd1.myworkdayjobs.com/SEL/job/Washington--...</t>
+        </is>
+      </c>
+      <c r="D381" s="6" t="inlineStr">
+        <is>
+          <t>shortlisted</t>
+        </is>
+      </c>
+      <c r="E381" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="F381" s="4" t="inlineStr">
+        <is>
+          <t>The job is an internship, so there is no experience gap. The candidate has relevant skills in Full Stack Development, AI Agents, LLM pipelines, Machine Learning, and Software Engineering, which aligns with the job requirements. The candidate's degree is currently enrolled, but they are open to relocation and sponsorship, which are not explicitly required by the job. The job does not explicitly require US Citizenship or Security Clearance, and it is not a senior/managerial role, so there are no auto-rejects. The candidate's experience and skills match the job requirements, and there are no domain penalties. The role title does not exactly match the candidate's target roles, but it is relevant, so no bonus is added.</t>
+        </is>
+      </c>
+      <c r="G381" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-07T02:20:26.164264</t>
+        </is>
+      </c>
+      <c r="H381" s="7" t="inlineStr">
+        <is>
+          <t>➜ Apply</t>
+        </is>
+      </c>
+    </row>
+    <row r="382" ht="28" customHeight="1">
+      <c r="A382" s="8" t="inlineStr">
+        <is>
+          <t>Game Research &amp; Development Intern - Engine Research</t>
+        </is>
+      </c>
+      <c r="B382" s="9" t="inlineStr">
+        <is>
+          <t>Tencent</t>
+        </is>
+      </c>
+      <c r="C382" s="10" t="inlineStr">
+        <is>
+          <t>https://tencent.wd1.myworkdayjobs.com/Tencent_Careers/job...</t>
+        </is>
+      </c>
+      <c r="D382" s="11" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="E382" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F382" s="9" t="inlineStr">
+        <is>
+          <t>Rejected: Non-US Location (London, UK)</t>
+        </is>
+      </c>
+      <c r="G382" s="9" t="inlineStr">
+        <is>
+          <t>2026-03-07T02:20:26.164264</t>
+        </is>
+      </c>
+      <c r="H382" s="7" t="inlineStr">
+        <is>
+          <t>➜ Apply</t>
+        </is>
+      </c>
+    </row>
+    <row r="383" ht="28" customHeight="1">
+      <c r="A383" s="3" t="inlineStr">
+        <is>
+          <t>Research Intern - Sustainable Architecture</t>
+        </is>
+      </c>
+      <c r="B383" s="4" t="inlineStr">
+        <is>
+          <t>Autodesk</t>
+        </is>
+      </c>
+      <c r="C383" s="5" t="inlineStr">
+        <is>
+          <t>https://autodesk.wd1.myworkdayjobs.com/uni/job/California...</t>
+        </is>
+      </c>
+      <c r="D383" s="6" t="inlineStr">
+        <is>
+          <t>shortlisted</t>
+        </is>
+      </c>
+      <c r="E383" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="F383" s="4" t="inlineStr">
+        <is>
+          <t>The job is for a Research Intern - Sustainable Architecture, which is not explicitly a senior or staff level position, so no auto-reject. The job does not explicitly require US Citizenship or Security Clearance. The candidate is a Master's student, so the experience gap is not applicable. The job does not mention any specific core tech stack that the candidate is missing. The domain is not in finance, legal tech, or non-tech companies, so no domain penalty. The role title does not exactly match the candidate's target roles, but it involves AI/ML work, so +1. The score is 8, which is above the candidate's threshold of 6, and the candidate is an intern, so no need for a full rewrite.</t>
+        </is>
+      </c>
+      <c r="G383" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-07T02:20:26.164264</t>
+        </is>
+      </c>
+      <c r="H383" s="7" t="inlineStr">
+        <is>
+          <t>➜ Apply</t>
+        </is>
+      </c>
+    </row>
+    <row r="384" ht="28" customHeight="1">
+      <c r="A384" s="3" t="inlineStr">
+        <is>
+          <t>Data Visualization Analyst Intern - Digital &amp; Data Analytics Team</t>
+        </is>
+      </c>
+      <c r="B384" s="4" t="inlineStr">
+        <is>
+          <t>Chemours</t>
+        </is>
+      </c>
+      <c r="C384" s="5" t="inlineStr">
+        <is>
+          <t>https://chemours.wd103.myworkdayjobs.com/Chemours/job/US-...</t>
+        </is>
+      </c>
+      <c r="D384" s="6" t="inlineStr">
+        <is>
+          <t>shortlisted</t>
+        </is>
+      </c>
+      <c r="E384" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="F384" s="4" t="inlineStr">
+        <is>
+          <t>The job does not explicitly require US Citizenship or Security Clearance, so no auto-reject. The job is an internship, so no experience gap deduction. The job does not mention any specific core tech stack mismatch, so no deduction for that. The domain is not in the non-tech categories, so no domain penalty. The role title does not exactly match the candidate's target roles, so no role relevance bonus. The candidate is enrolled in a Master's program, which is not a requirement, so no additional deductions.</t>
+        </is>
+      </c>
+      <c r="G384" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-07T02:20:26.164264</t>
+        </is>
+      </c>
+      <c r="H384" s="7" t="inlineStr">
+        <is>
+          <t>➜ Apply</t>
+        </is>
+      </c>
+    </row>
+    <row r="385" ht="28" customHeight="1">
+      <c r="A385" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineer Co-op - AI/Data</t>
+        </is>
+      </c>
+      <c r="B385" s="4" t="inlineStr">
+        <is>
+          <t>Rolls Royce</t>
+        </is>
+      </c>
+      <c r="C385" s="5" t="inlineStr">
+        <is>
+          <t>https://jobs.bmwgroup.com/job/Greenville-FG-AM-61-Softwar...</t>
+        </is>
+      </c>
+      <c r="D385" s="6" t="inlineStr">
+        <is>
+          <t>shortlisted</t>
+        </is>
+      </c>
+      <c r="E385" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="F385" s="4" t="inlineStr">
+        <is>
+          <t>The job does not explicitly require US Citizenship or a Security Clearance, so no auto-reject occurs. The job requires 3-4 years of experience, which deducts 2 points. The job does not mention any specific core tech stack mismatch, so no deductions apply. The job is in the AI/Data domain, which does not incur a domain penalty. The role title 'Software Engineer Co-op - AI/Data' matches the candidate's target roles, so a +1 bonus is applied. The final score is 8, which meets the candidate's score threshold of 6.</t>
+        </is>
+      </c>
+      <c r="G385" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-07T02:20:26.164264</t>
+        </is>
+      </c>
+      <c r="H385" s="7" t="inlineStr">
+        <is>
+          <t>➜ Apply</t>
+        </is>
+      </c>
+    </row>
+    <row r="386" ht="28" customHeight="1">
+      <c r="A386" s="3" t="inlineStr">
+        <is>
+          <t>IT Innovation &amp; Research Intern</t>
+        </is>
+      </c>
+      <c r="B386" s="4" t="inlineStr">
+        <is>
+          <t>Rolls Royce</t>
+        </is>
+      </c>
+      <c r="C386" s="5" t="inlineStr">
+        <is>
+          <t>https://jobs.bmwgroup.com/job/Greenville-IT-Innovation-&amp;-...</t>
+        </is>
+      </c>
+      <c r="D386" s="6" t="inlineStr">
+        <is>
+          <t>shortlisted</t>
+        </is>
+      </c>
+      <c r="E386" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="F386" s="4" t="inlineStr">
+        <is>
+          <t>The job does not explicitly require US Citizenship or a Security Clearance, so no auto-reject. The job is an internship, so no experience gap deduction. The job requires a degree in Computer Science, Computer Engineering, Mathematics, Statistics, or related discipline, and the candidate has a Master of Computer Science, so no core tech stack mismatch. The job is in the tech domain, so no domain penalty. The role title does not exactly match the candidate's target roles, so no role relevance bonus. The candidate is enrolled in a degree program and can work full-time on-site, so they meet the qualifications. The job requires a substance abuse test, which is not a dealbreaker for the candidate's visa status.</t>
+        </is>
+      </c>
+      <c r="G386" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-07T02:20:26.164264</t>
+        </is>
+      </c>
+      <c r="H386" s="7" t="inlineStr">
+        <is>
+          <t>➜ Apply</t>
+        </is>
+      </c>
+    </row>
+    <row r="387" ht="28" customHeight="1">
+      <c r="A387" s="3" t="inlineStr">
+        <is>
+          <t>Paint Shop Quality Intern</t>
+        </is>
+      </c>
+      <c r="B387" s="4" t="inlineStr">
+        <is>
+          <t>Rolls Royce</t>
+        </is>
+      </c>
+      <c r="C387" s="5" t="inlineStr">
+        <is>
+          <t>https://jobs.bmwgroup.com/job/Greer-Paint-Shop-Quality-In...</t>
+        </is>
+      </c>
+      <c r="D387" s="6" t="inlineStr">
+        <is>
+          <t>shortlisted</t>
+        </is>
+      </c>
+      <c r="E387" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="F387" s="4" t="inlineStr">
+        <is>
+          <t>The job is explicitly for an intern position, so there is no experience gap. The job does not require any specific core tech stack, so no deductions apply there. The domain is manufacturing, which is not tech-related, so a -3 penalty applies. The role title does not match the candidate's target roles, so no bonus is added. The candidate is enrolled in a Master's program, which meets the educational requirement, and they are open to on-site work, so there are no additional deductions. The candidate's visa status is not relevant to this job, and the job does not explicitly require US citizenship or a security clearance.</t>
+        </is>
+      </c>
+      <c r="G387" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-07T02:20:26.164264</t>
+        </is>
+      </c>
+      <c r="H387" s="7" t="inlineStr">
+        <is>
+          <t>➜ Apply</t>
+        </is>
+      </c>
+    </row>
+    <row r="388" ht="28" customHeight="1">
+      <c r="A388" s="3" t="inlineStr">
+        <is>
+          <t>Predictive Maintenance Co-op</t>
+        </is>
+      </c>
+      <c r="B388" s="4" t="inlineStr">
+        <is>
+          <t>Rolls Royce</t>
+        </is>
+      </c>
+      <c r="C388" s="5" t="inlineStr">
+        <is>
+          <t>https://jobs.bmwgroup.com/job/Spartanburg-Predictive-Main...</t>
+        </is>
+      </c>
+      <c r="D388" s="6" t="inlineStr">
+        <is>
+          <t>shortlisted</t>
+        </is>
+      </c>
+      <c r="E388" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="F388" s="4" t="inlineStr">
+        <is>
+          <t>The job is explicitly for an intern/co-op position, which does not trigger an auto-reject. The candidate has relevant experience in Full Stack Development, AI Agents, LLM pipelines, Machine Learning, and Software Engineering, which aligns with the job requirements. The job does not explicitly require 5+ years of experience, so no deduction is applied here. The job is in the manufacturing domain, which does not trigger a domain penalty. The candidate's target roles include internships, which match the job title. The candidate's skills and experience are well-aligned with the job requirements, including experience with Python, Java, C++, and other relevant technologies. The candidate's visa status is not an issue as the job does not explicitly require US Citizenship or Security Clearance.</t>
+        </is>
+      </c>
+      <c r="G388" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-07T02:20:26.164264</t>
+        </is>
+      </c>
+      <c r="H388" s="7" t="inlineStr">
+        <is>
+          <t>➜ Apply</t>
+        </is>
+      </c>
+    </row>
+    <row r="389" ht="28" customHeight="1">
+      <c r="A389" s="3" t="inlineStr">
+        <is>
+          <t>Innovations Software Developer Intern</t>
+        </is>
+      </c>
+      <c r="B389" s="4" t="inlineStr">
+        <is>
+          <t>Rolls Royce</t>
+        </is>
+      </c>
+      <c r="C389" s="5" t="inlineStr">
+        <is>
+          <t>https://jobs.bmwgroup.com/job/Spartanburg-TX-S-12-Innovat...</t>
+        </is>
+      </c>
+      <c r="D389" s="6" t="inlineStr">
+        <is>
+          <t>shortlisted</t>
+        </is>
+      </c>
+      <c r="E389" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="F389" s="4" t="inlineStr">
+        <is>
+          <t>The job does not explicitly require US Citizenship or Security Clearance, so no auto-reject. The job requires 5+ years of experience, which is a deduction of -3. The job does not mention any specific core tech stack mismatch, so no deduction for that. The job is in the automotive industry, which is not a non-tech company, so no domain penalty. The role title does not match the candidate's target roles exactly, so no role relevance bonus. The candidate's experience level is a degree program, which is not an internship, so no additional deductions or bonuses.</t>
+        </is>
+      </c>
+      <c r="G389" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-07T02:20:26.164264</t>
+        </is>
+      </c>
+      <c r="H389" s="7" t="inlineStr">
+        <is>
+          <t>➜ Apply</t>
+        </is>
+      </c>
+    </row>
+    <row r="390" ht="28" customHeight="1">
+      <c r="A390" s="3" t="inlineStr">
+        <is>
+          <t>Paint Shop Digitalization Co-op</t>
+        </is>
+      </c>
+      <c r="B390" s="4" t="inlineStr">
+        <is>
+          <t>Rolls Royce</t>
+        </is>
+      </c>
+      <c r="C390" s="5" t="inlineStr">
+        <is>
+          <t>https://jobs.bmwgroup.com/job/Spartanburg-Paint-Shop-Digi...</t>
+        </is>
+      </c>
+      <c r="D390" s="6" t="inlineStr">
+        <is>
+          <t>shortlisted</t>
+        </is>
+      </c>
+      <c r="E390" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="F390" s="4" t="inlineStr">
+        <is>
+          <t>The job does not explicitly require US Citizenship or a Security Clearance, so it does not auto-reject. The job requires 3-4 years of experience, which deducts -2. The job is not in a domain that incurs a penalty, such as finance or legal tech. The role title does not match the candidate's target roles exactly, so no bonus is added. The candidate's experience and skills align well with the job requirements, but the job requires on-site work, which the candidate is open to but may need to be adjusted.</t>
+        </is>
+      </c>
+      <c r="G390" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-07T02:20:26.164264</t>
+        </is>
+      </c>
+      <c r="H390" s="7" t="inlineStr">
+        <is>
+          <t>➜ Apply</t>
+        </is>
+      </c>
+    </row>
+    <row r="391" ht="28" customHeight="1">
+      <c r="A391" s="3" t="inlineStr">
+        <is>
+          <t>Paint Shop Digitalization Developer Maintenance Planning Intern</t>
+        </is>
+      </c>
+      <c r="B391" s="4" t="inlineStr">
+        <is>
+          <t>Rolls Royce</t>
+        </is>
+      </c>
+      <c r="C391" s="5" t="inlineStr">
+        <is>
+          <t>https://jobs.bmwgroup.com/job/Spartanburg-Paint-Shop-Digi...</t>
+        </is>
+      </c>
+      <c r="D391" s="6" t="inlineStr">
+        <is>
+          <t>shortlisted</t>
+        </is>
+      </c>
+      <c r="E391" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="F391" s="4" t="inlineStr">
+        <is>
+          <t>The job does not explicitly require US Citizenship or a Security Clearance, so it does not auto-reject. The job requires 3-4 years of experience, which deducts 2 points. The job does not mention any specific core tech stack that the candidate is missing, so no deductions apply here. The job is not in a domain that incurs a penalty. The role title does not match the candidate's target roles exactly, so no bonus is added. The candidate is enrolled in a Master's program, which meets the educational requirement, and the job does not require 5+ years of experience, so no further deductions apply.</t>
+        </is>
+      </c>
+      <c r="G391" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-07T02:20:26.164264</t>
+        </is>
+      </c>
+      <c r="H391" s="7" t="inlineStr">
+        <is>
+          <t>➜ Apply</t>
+        </is>
+      </c>
+    </row>
+    <row r="392" ht="28" customHeight="1">
+      <c r="A392" s="8" t="inlineStr">
+        <is>
+          <t>Quality Software Intern</t>
+        </is>
+      </c>
+      <c r="B392" s="9" t="inlineStr">
+        <is>
+          <t>Rolls Royce</t>
+        </is>
+      </c>
+      <c r="C392" s="10" t="inlineStr">
+        <is>
+          <t>https://jobs.bmwgroup.com/job/Greer-MN-80-Quality-Softwar...</t>
+        </is>
+      </c>
+      <c r="D392" s="11" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="E392" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F392" s="9" t="inlineStr">
+        <is>
+          <t>The job explicitly requires US Citizenship or Security Clearance, which is an auto-reject criterion. The job also requires on-site full-time work, which the candidate is open to but does not specify. The job does not explicitly require 5+ years of experience, so no deductions apply for experience gap. There are no core tech stack mismatches as the candidate has relevant skills. The domain is not in a non-tech company, finance/banking, or pure software/AI/ML company, so no domain penalty applies. The role title does not match the candidate's target roles exactly, but it involves software engineering, which adds a +1. The candidate's score is 0 due to the auto-reject criteria.</t>
+        </is>
+      </c>
+      <c r="G392" s="9" t="inlineStr">
+        <is>
+          <t>2026-03-07T02:20:26.164264</t>
+        </is>
+      </c>
+      <c r="H392" s="7" t="inlineStr">
+        <is>
+          <t>➜ Apply</t>
+        </is>
+      </c>
+    </row>
+    <row r="393" ht="28" customHeight="1">
+      <c r="A393" s="3" t="inlineStr">
+        <is>
+          <t>The Data School - Data Analyst Consultant</t>
+        </is>
+      </c>
+      <c r="B393" s="4" t="inlineStr">
+        <is>
+          <t>The Information Lab</t>
+        </is>
+      </c>
+      <c r="C393" s="5" t="inlineStr">
+        <is>
+          <t>https://jobs.lever.co/theinformationlab/eaa64bb6-30b9-44b...</t>
+        </is>
+      </c>
+      <c r="D393" s="6" t="inlineStr">
+        <is>
+          <t>shortlisted</t>
+        </is>
+      </c>
+      <c r="E393" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="F393" s="4" t="inlineStr">
+        <is>
+          <t>The job does not explicitly require US Citizenship or Security Clearance, so no auto-reject occurs. The job is not a senior or staff level role, so no auto-reject occurs. The job does not explicitly require 3-4 or 5+ years of experience, so no experience gap deductions apply. The job does not mention any specific core technologies that the candidate is missing, so no core tech stack mismatch deductions apply. The job is not in a domain that incurs a penalty, so no domain penalty deductions apply. The role title does not match the candidate's target roles exactly, so no role relevance bonus is added. The score is 10, which is above the candidate's threshold of 6, but no role relevance bonus is added.</t>
+        </is>
+      </c>
+      <c r="G393" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-07T02:20:26.164264</t>
+        </is>
+      </c>
+      <c r="H393" s="7" t="inlineStr">
+        <is>
+          <t>➜ Apply</t>
+        </is>
+      </c>
+    </row>
+    <row r="394" ht="28" customHeight="1">
+      <c r="A394" s="8" t="inlineStr">
+        <is>
+          <t>Data Analyst Intern</t>
+        </is>
+      </c>
+      <c r="B394" s="9" t="inlineStr">
+        <is>
+          <t>Telligen</t>
+        </is>
+      </c>
+      <c r="C394" s="10" t="inlineStr">
+        <is>
+          <t>https://jobs.lever.co/telligen/748abf57-b18c-44a2-acef-f9...</t>
+        </is>
+      </c>
+      <c r="D394" s="11" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="E394" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="F394" s="9" t="inlineStr">
+        <is>
+          <t>The job is explicitly for a Data Analyst Intern, which does not match the candidate's target roles. The job does not require 5+ years of experience, so no deductions are applied under STEP 2. There are no core tech stack mismatches, so no deductions are applied under STEP 3. The job is not in a non-tech company, finance/banking, or a pure software/AI/ML company, so no deductions are applied under STEP 4. The candidate is not required to have US citizenship or a security clearance, so no deductions are applied under STEP 1. The candidate's experience and skills are not directly relevant to the role, but the candidate is an intern, so no additional penalties apply. The score is below the threshold of 6, so the candidate does not meet the score threshold.</t>
+        </is>
+      </c>
+      <c r="G394" s="9" t="inlineStr">
+        <is>
+          <t>2026-03-07T02:20:26.164264</t>
+        </is>
+      </c>
+      <c r="H394" s="7" t="inlineStr">
+        <is>
+          <t>➜ Apply</t>
+        </is>
+      </c>
+    </row>
+    <row r="395" ht="28" customHeight="1">
+      <c r="A395" s="3" t="inlineStr">
+        <is>
+          <t>Software Development Intern</t>
+        </is>
+      </c>
+      <c r="B395" s="4" t="inlineStr">
+        <is>
+          <t>Telligen</t>
+        </is>
+      </c>
+      <c r="C395" s="5" t="inlineStr">
+        <is>
+          <t>https://jobs.lever.co/telligen/d75b8773-9d78-49f8-9cc9-28...</t>
+        </is>
+      </c>
+      <c r="D395" s="6" t="inlineStr">
+        <is>
+          <t>shortlisted</t>
+        </is>
+      </c>
+      <c r="E395" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="F395" s="4" t="inlineStr">
+        <is>
+          <t>Auto-Shortlisted (Protected Title)</t>
+        </is>
+      </c>
+      <c r="G395" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-07T02:20:26.164264</t>
+        </is>
+      </c>
+      <c r="H395" s="7" t="inlineStr">
+        <is>
+          <t>➜ Apply</t>
+        </is>
+      </c>
+    </row>
+    <row r="396" ht="28" customHeight="1">
+      <c r="A396" s="8" t="inlineStr">
+        <is>
+          <t>SVG Software Intern</t>
+        </is>
+      </c>
+      <c r="B396" s="9" t="inlineStr">
+        <is>
+          <t>Cadence Design Systems</t>
+        </is>
+      </c>
+      <c r="C396" s="10" t="inlineStr">
+        <is>
+          <t>https://cadence.wd1.myworkdayjobs.com/University_Talent_I...</t>
+        </is>
+      </c>
+      <c r="D396" s="11" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="E396" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="F396" s="9" t="inlineStr">
+        <is>
+          <t>[PRE-CHECK] Quant firm — auto-capped at 2.</t>
+        </is>
+      </c>
+      <c r="G396" s="9" t="inlineStr">
+        <is>
+          <t>2026-03-07T02:20:26.164264</t>
+        </is>
+      </c>
+      <c r="H396" s="7" t="inlineStr">
+        <is>
+          <t>➜ Apply</t>
+        </is>
+      </c>
+    </row>
+    <row r="397" ht="28" customHeight="1">
+      <c r="A397" s="3" t="inlineStr">
+        <is>
+          <t>AI Analyst Intern</t>
+        </is>
+      </c>
+      <c r="B397" s="4" t="inlineStr">
+        <is>
+          <t>Logitech</t>
+        </is>
+      </c>
+      <c r="C397" s="5" t="inlineStr">
+        <is>
+          <t>https://logitech.wd5.myworkdayjobs.com/Logitech/job/Camas...</t>
+        </is>
+      </c>
+      <c r="D397" s="6" t="inlineStr">
+        <is>
+          <t>shortlisted</t>
+        </is>
+      </c>
+      <c r="E397" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="F397" s="4" t="inlineStr">
+        <is>
+          <t>The job title is 'AI Analyst Intern', which is an internship role, so no experience gap deduction applies. The job does not explicitly require US Citizenship or Security Clearance, and it is an internship role, so no auto-rejects apply. The candidate has relevant skills in AI/ML, including PyTorch, TensorFlow, and NLP, which are not explicitly required but are beneficial. The job is in the tech domain, so no domain penalty applies. The candidate's role title does not match exactly, but it is close to 'AI Engineer Intern', which is a relevant role, so a +1 bonus is applied.</t>
+        </is>
+      </c>
+      <c r="G397" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-07T02:20:26.164264</t>
+        </is>
+      </c>
+      <c r="H397" s="7" t="inlineStr">
+        <is>
+          <t>➜ Apply</t>
+        </is>
+      </c>
+    </row>
+    <row r="398" ht="28" customHeight="1">
+      <c r="A398" s="3" t="inlineStr">
+        <is>
+          <t>Data Analyst Intern - Wildfire Risk Suite</t>
+        </is>
+      </c>
+      <c r="B398" s="4" t="inlineStr">
+        <is>
+          <t>Precisely</t>
+        </is>
+      </c>
+      <c r="C398" s="5" t="inlineStr">
+        <is>
+          <t>https://www.precisely.com/careers-and-culture/us-jobs/job...</t>
+        </is>
+      </c>
+      <c r="D398" s="6" t="inlineStr">
+        <is>
+          <t>shortlisted</t>
+        </is>
+      </c>
+      <c r="E398" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="F398" s="4" t="inlineStr">
+        <is>
+          <t>The job is for a Data Analyst Intern, which is an internship role, so no experience gap deduction applies. The candidate's skills and experience do not match the core tech stack required for the role, and the job is in a tech domain, so no domain penalty applies. The candidate's target roles include internships, but the role title does not match exactly, so no role relevance bonus applies. The candidate's score is 7, which meets the score threshold of 6, but the role title does not match exactly, so the strategy is 'skills_only'.</t>
+        </is>
+      </c>
+      <c r="G398" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-07T02:20:26.165774</t>
+        </is>
+      </c>
+      <c r="H398" s="7" t="inlineStr">
+        <is>
+          <t>➜ Apply</t>
+        </is>
+      </c>
+    </row>
+    <row r="399" ht="28" customHeight="1">
+      <c r="A399" s="8" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer Intern</t>
+        </is>
+      </c>
+      <c r="B399" s="9" t="inlineStr">
+        <is>
+          <t>Unlikely AI</t>
+        </is>
+      </c>
+      <c r="C399" s="10" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/unlikelyai/8d50b0a8-0f5c-403e-86...</t>
+        </is>
+      </c>
+      <c r="D399" s="11" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="E399" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F399" s="9" t="inlineStr">
+        <is>
+          <t>Rejected: Non-US Location (London, UK)</t>
+        </is>
+      </c>
+      <c r="G399" s="9" t="inlineStr">
+        <is>
+          <t>2026-03-07T02:20:26.165774</t>
+        </is>
+      </c>
+      <c r="H399" s="7" t="inlineStr">
+        <is>
+          <t>➜ Apply</t>
+        </is>
+      </c>
+    </row>
+    <row r="400" ht="28" customHeight="1">
+      <c r="A400" s="3" t="inlineStr">
+        <is>
+          <t>Kernel Engineer – Intern and Full-time</t>
+        </is>
+      </c>
+      <c r="B400" s="4" t="inlineStr">
+        <is>
+          <t>Tilde Research</t>
+        </is>
+      </c>
+      <c r="C400" s="5" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/tilderesearch/bc4e4071-cf64-4460...</t>
+        </is>
+      </c>
+      <c r="D400" s="6" t="inlineStr">
+        <is>
+          <t>shortlisted</t>
+        </is>
+      </c>
+      <c r="E400" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="F400" s="4" t="inlineStr">
+        <is>
+          <t>The job is for a Kernel Engineer – Intern and Full-time, which does not explicitly require US Citizenship or Security Clearance, so it does not auto-reject. The job does not specify a required experience level, so no experience gap deduction applies. There are no core tech stack mismatches as the candidate has experience with Cuda, which is a relevant technology. The job is in a tech company, so no domain penalty applies. The role title does not exactly match the candidate's target roles, but it involves technical work, so a +1 is added. The candidate's experience level is an internship, which is appropriate for the job.</t>
+        </is>
+      </c>
+      <c r="G400" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-07T02:20:26.165774</t>
+        </is>
+      </c>
+      <c r="H400" s="7" t="inlineStr">
+        <is>
+          <t>➜ Apply</t>
+        </is>
+      </c>
+    </row>
+    <row r="401" ht="28" customHeight="1">
+      <c r="A401" s="3" t="inlineStr">
+        <is>
+          <t>ML Researcher – Intern and Full-time</t>
+        </is>
+      </c>
+      <c r="B401" s="4" t="inlineStr">
+        <is>
+          <t>Tilde Research</t>
+        </is>
+      </c>
+      <c r="C401" s="5" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/tilderesearch/e850d5b0-a5d6-4b9c...</t>
+        </is>
+      </c>
+      <c r="D401" s="6" t="inlineStr">
+        <is>
+          <t>shortlisted</t>
+        </is>
+      </c>
+      <c r="E401" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="F401" s="4" t="inlineStr">
+        <is>
+          <t>The job does not explicitly require US Citizenship or Security Clearance, so no auto-reject. The job is for an Intern, which does not require 3-4 or 5+ years of experience, so no experience gap deduction. The job does not mention any specific core tech stack that the candidate is missing, so no core tech stack mismatch deduction. The job is in the ML domain, which is not a domain penalty. The role title does not exactly match the candidate's target roles, but it involves AI/ML work, so a +1 is added. The candidate is enrolled in a Master's program and requires sponsorship, which aligns with the job's requirements, so no additional deductions are applied.</t>
+        </is>
+      </c>
+      <c r="G401" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-07T02:20:26.165774</t>
+        </is>
+      </c>
+      <c r="H401" s="7" t="inlineStr">
+        <is>
+          <t>➜ Apply</t>
+        </is>
+      </c>
+    </row>
+    <row r="402" ht="28" customHeight="1">
+      <c r="A402" s="3" t="inlineStr">
+        <is>
+          <t>ML Engineer</t>
+        </is>
+      </c>
+      <c r="B402" s="4" t="inlineStr">
+        <is>
+          <t>Tilde Research</t>
+        </is>
+      </c>
+      <c r="C402" s="5" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/tilderesearch/b2e145db-0111-47c1...</t>
+        </is>
+      </c>
+      <c r="D402" s="6" t="inlineStr">
+        <is>
+          <t>shortlisted</t>
+        </is>
+      </c>
+      <c r="E402" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="F402" s="4" t="inlineStr">
+        <is>
+          <t>The job does not explicitly require US Citizenship or Security Clearance, so no auto-reject. The job requires 3-4 years of experience, so no deduction for experience gap. The candidate has experience with PyTorch and TensorFlow, which are core technologies required for the role, so no deduction for core tech stack mismatch. The job is in the tech domain, so no domain penalty. The role title 'ML Engineer' matches the candidate's target roles, so +1. The candidate's experience and skills are relevant to the role, so no further adjustments needed.</t>
+        </is>
+      </c>
+      <c r="G402" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-07T02:20:26.165774</t>
+        </is>
+      </c>
+      <c r="H402" s="7" t="inlineStr">
+        <is>
+          <t>➜ Apply</t>
+        </is>
+      </c>
+    </row>
+    <row r="403" ht="28" customHeight="1">
+      <c r="A403" s="8" t="inlineStr">
+        <is>
+          <t>Software Engineer Intern</t>
+        </is>
+      </c>
+      <c r="B403" s="9" t="inlineStr">
+        <is>
+          <t>Unlikely AI</t>
+        </is>
+      </c>
+      <c r="C403" s="10" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/unlikelyai/a0f38397-9feb-407c-bb...</t>
+        </is>
+      </c>
+      <c r="D403" s="11" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="E403" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F403" s="9" t="inlineStr">
+        <is>
+          <t>Rejected: Non-US Location (London, UK)</t>
+        </is>
+      </c>
+      <c r="G403" s="9" t="inlineStr">
+        <is>
+          <t>2026-03-07T02:20:26.165774</t>
+        </is>
+      </c>
+      <c r="H403" s="7" t="inlineStr">
+        <is>
+          <t>➜ Apply</t>
+        </is>
+      </c>
+    </row>
+    <row r="404" ht="28" customHeight="1">
+      <c r="A404" s="3" t="inlineStr">
+        <is>
+          <t>Intern - AI and Machine Learning</t>
+        </is>
+      </c>
+      <c r="B404" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Coherent </t>
+        </is>
+      </c>
+      <c r="C404" s="5" t="inlineStr">
+        <is>
+          <t>https://hcwp.fa.us2.oraclecloud.com/hcmUI/CandidateExperi...</t>
+        </is>
+      </c>
+      <c r="D404" s="6" t="inlineStr">
+        <is>
+          <t>shortlisted</t>
+        </is>
+      </c>
+      <c r="E404" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="F404" s="4" t="inlineStr">
+        <is>
+          <t>The job is explicitly for an Intern - AI and Machine Learning, which matches the candidate's target roles. The job does not explicitly require US Citizenship or Security Clearance. The job requires 3-4 years of experience, which is not applicable since the candidate is a student. The core tech stack mismatch is 2 (missing PyTorch and TensorFlow). The domain is in AI and Machine Learning, which is relevant. The candidate's experience and skills align well with the job requirements, and the candidate is open to on-site work in Saxonburg, PA.</t>
+        </is>
+      </c>
+      <c r="G404" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-07T02:20:26.165774</t>
+        </is>
+      </c>
+      <c r="H404" s="7" t="inlineStr">
+        <is>
+          <t>➜ Apply</t>
+        </is>
+      </c>
+    </row>
+    <row r="405" ht="28" customHeight="1">
+      <c r="A405" s="3" t="inlineStr">
+        <is>
+          <t>Full Stack Engineer Intern</t>
+        </is>
+      </c>
+      <c r="B405" s="4" t="inlineStr">
+        <is>
+          <t>Unwrap</t>
+        </is>
+      </c>
+      <c r="C405" s="5" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/Unwrap/aa875007-108e-492b-86ad-1...</t>
+        </is>
+      </c>
+      <c r="D405" s="6" t="inlineStr">
+        <is>
+          <t>shortlisted</t>
+        </is>
+      </c>
+      <c r="E405" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="F405" s="4" t="inlineStr">
+        <is>
+          <t>The job is explicitly for an Internship, which does not trigger any auto-reject. The candidate has Full Stack Development experience, which matches the job requirements. The candidate has experience with Python, Java, C++, TypeScript, JavaScript, SQL, Go, React, Next.js, Node.js, FastAPI, and other relevant technologies, which aligns well with the job. The candidate is enrolled in a Master of Computer Science, which is relevant. The job is on-site, which the candidate is open to. The job does not require 5+ years of experience, and the candidate is an intern, so there is no experience gap. There are no core tech stack mismatches. The job is in the tech domain, so there is no domain penalty. The role title does not exactly match the candidate's target roles, but it is close, so no bonus is added.</t>
+        </is>
+      </c>
+      <c r="G405" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-07T02:20:26.165774</t>
+        </is>
+      </c>
+      <c r="H405" s="7" t="inlineStr">
+        <is>
+          <t>➜ Apply</t>
+        </is>
+      </c>
+    </row>
+    <row r="406" ht="28" customHeight="1">
+      <c r="A406" s="8" t="inlineStr">
+        <is>
+          <t>Level 4 Data Analyst Apprenticeship</t>
+        </is>
+      </c>
+      <c r="B406" s="9" t="inlineStr">
+        <is>
+          <t>The Walt Disney Company</t>
+        </is>
+      </c>
+      <c r="C406" s="10" t="inlineStr">
+        <is>
+          <t>https://disney.wd5.myworkdayjobs.com/disneycareerdc/job/L...</t>
+        </is>
+      </c>
+      <c r="D406" s="11" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="E406" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F406" s="9" t="inlineStr">
+        <is>
+          <t>Rejected: Non-US Location (London, UK)</t>
+        </is>
+      </c>
+      <c r="G406" s="9" t="inlineStr">
+        <is>
+          <t>2026-03-07T02:20:26.165774</t>
+        </is>
+      </c>
+      <c r="H406" s="7" t="inlineStr">
+        <is>
+          <t>➜ Apply</t>
+        </is>
+      </c>
+    </row>
+    <row r="407" ht="28" customHeight="1">
+      <c r="A407" s="3" t="inlineStr">
+        <is>
+          <t>Data Analyst Intern-1</t>
+        </is>
+      </c>
+      <c r="B407" s="4" t="inlineStr">
+        <is>
+          <t>Intermountain Healthcare</t>
+        </is>
+      </c>
+      <c r="C407" s="5" t="inlineStr">
+        <is>
+          <t>https://imh.wd108.myworkdayjobs.com/IntermountainCareers/...</t>
+        </is>
+      </c>
+      <c r="D407" s="6" t="inlineStr">
+        <is>
+          <t>shortlisted</t>
+        </is>
+      </c>
+      <c r="E407" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="F407" s="4" t="inlineStr">
+        <is>
+          <t>The job is explicitly for a Data Analyst Intern-1, which is an internship role. The candidate is targeting internships and the job description aligns with the candidate's experience level. There are no core tech stack mismatches, and the domain is non-tech, but the score is capped at 10. The candidate's visa status is not a concern as the job does not require US Citizenship or Security Clearance. The job does not explicitly require 5+ years of experience, so no deductions apply here. The candidate's experience and skills are relevant to the role, but the job description does not explicitly mention AI/ML or LLM work, so no bonus is added.</t>
+        </is>
+      </c>
+      <c r="G407" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-07T02:20:26.165774</t>
+        </is>
+      </c>
+      <c r="H407" s="7" t="inlineStr">
+        <is>
+          <t>➜ Apply</t>
+        </is>
+      </c>
+    </row>
+    <row r="408" ht="28" customHeight="1">
+      <c r="A408" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineering Intern</t>
+        </is>
+      </c>
+      <c r="B408" s="4" t="inlineStr">
+        <is>
+          <t>Arch Capital Group</t>
+        </is>
+      </c>
+      <c r="C408" s="5" t="inlineStr">
+        <is>
+          <t>https://archgroup.wd1.myworkdayjobs.com/careers/job/Jerse...</t>
+        </is>
+      </c>
+      <c r="D408" s="6" t="inlineStr">
+        <is>
+          <t>shortlisted</t>
+        </is>
+      </c>
+      <c r="E408" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="F408" s="4" t="inlineStr">
+        <is>
+          <t>The job is for a Software Engineering Intern, which is an internship level position, so no auto-reject occurs. The candidate has relevant experience in Full Stack Development, AI Agents, LLM pipelines, and Machine Learning, which aligns with the job requirements. The candidate's skills in Python, Java, C++, TypeScript, JavaScript, and key AI/ML tools like PyTorch and TensorFlow are relevant. The company is in the insurance and reinsurance industry, which is not a non-tech company, so no domain penalty applies. The candidate's preference for internship roles and the job being an internship match, so no role relevance bonus is added. The candidate's score is 8 after considering the experience and skills match, but no domain penalty or role relevance bonus.</t>
+        </is>
+      </c>
+      <c r="G408" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-07T02:20:26.165774</t>
+        </is>
+      </c>
+      <c r="H408" s="7" t="inlineStr">
+        <is>
+          <t>➜ Apply</t>
+        </is>
+      </c>
+    </row>
+    <row r="409" ht="28" customHeight="1">
+      <c r="A409" s="3" t="inlineStr">
+        <is>
+          <t>Embedded Software Engineering Intern</t>
+        </is>
+      </c>
+      <c r="B409" s="4" t="inlineStr">
+        <is>
+          <t>Ultra Maritime</t>
+        </is>
+      </c>
+      <c r="C409" s="5" t="inlineStr">
+        <is>
+          <t>https://ultra.wd3.myworkdayjobs.com/en-US/ultra-careers/j...</t>
+        </is>
+      </c>
+      <c r="D409" s="6" t="inlineStr">
+        <is>
+          <t>shortlisted</t>
+        </is>
+      </c>
+      <c r="E409" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="F409" s="4" t="inlineStr">
+        <is>
+          <t>The job is for an Embedded Software Engineering Intern, which is an internship level position, so no auto-reject occurs. The candidate has relevant experience in Full Stack Development, AI Agents, and Machine Learning, but the job requires specific embedded software experience, which is a core tech mismatch. There is no domain penalty as the company is in the tech sector. The role title does not match the candidate's target roles exactly, so no role relevance bonus is added.</t>
+        </is>
+      </c>
+      <c r="G409" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-07T02:20:26.165774</t>
+        </is>
+      </c>
+      <c r="H409" s="7" t="inlineStr">
+        <is>
+          <t>➜ Apply</t>
+        </is>
+      </c>
+    </row>
+    <row r="410" ht="28" customHeight="1">
+      <c r="A410" s="3" t="inlineStr">
+        <is>
+          <t>Software Developer Intern</t>
+        </is>
+      </c>
+      <c r="B410" s="4" t="inlineStr">
+        <is>
+          <t>iPipeline</t>
+        </is>
+      </c>
+      <c r="C410" s="5" t="inlineStr">
+        <is>
+          <t>https://careers-ipipeline.icims.com/jobs/1596/software-de...</t>
+        </is>
+      </c>
+      <c r="D410" s="6" t="inlineStr">
+        <is>
+          <t>shortlisted</t>
+        </is>
+      </c>
+      <c r="E410" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="F410" s="4" t="inlineStr">
+        <is>
+          <t>[SPONSORED] The job is for a Software Developer Intern, which is an internship level position, so no auto-reject occurs. The job does not explicitly require 3-4 years of experience, so no deduction for experience gap. The job does not mention any specific core tech stack that the candidate is missing, so no deduction for core tech stack mismatch. The job is in the financial services domain, which is not explicitly a non-tech company, so no domain penalty. The role title does not match the candidate's target roles exactly, but it involves software engineering work, so no bonus is added. The candidate's visa status requires sponsorship, which is not explicitly mentioned in the job description, so no additional deductions or bonuses are applied.</t>
+        </is>
+      </c>
+      <c r="G410" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-07T02:20:26.165774</t>
+        </is>
+      </c>
+      <c r="H410" s="7" t="inlineStr">
+        <is>
+          <t>➜ Apply</t>
+        </is>
+      </c>
+    </row>
+    <row r="411" ht="28" customHeight="1">
+      <c r="A411" s="3" t="inlineStr">
+        <is>
+          <t>Software Developer Intern</t>
+        </is>
+      </c>
+      <c r="B411" s="4" t="inlineStr">
+        <is>
+          <t>iPipeline</t>
+        </is>
+      </c>
+      <c r="C411" s="5" t="inlineStr">
+        <is>
+          <t>https://careers-ipipeline.icims.com/jobs/1591/software-de...</t>
+        </is>
+      </c>
+      <c r="D411" s="6" t="inlineStr">
+        <is>
+          <t>shortlisted</t>
+        </is>
+      </c>
+      <c r="E411" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="F411" s="4" t="inlineStr">
+        <is>
+          <t>[SPONSORED] The job is for a Software Developer Intern, which is an internship level position, so no auto-reject occurs. The job does not explicitly require 3-4 years of experience, so no deduction for experience gap. The job does not mention any specific core tech stack that the candidate is missing, so no deduction for core tech stack mismatch. The job is in the financial services domain, which is not explicitly a non-tech company, so no domain penalty. The role title does not match the candidate's target roles exactly, but it involves software engineering work, so no bonus is added. The candidate's visa status requires sponsorship, which is not explicitly mentioned in the job description, so no additional deductions or bonuses are applied.</t>
+        </is>
+      </c>
+      <c r="G411" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-07T02:20:26.165774</t>
+        </is>
+      </c>
+      <c r="H411" s="7" t="inlineStr">
+        <is>
+          <t>➜ Apply</t>
+        </is>
+      </c>
+    </row>
+    <row r="412" ht="28" customHeight="1">
+      <c r="A412" s="3" t="inlineStr">
+        <is>
+          <t>Data Science Intern</t>
+        </is>
+      </c>
+      <c r="B412" s="4" t="inlineStr">
+        <is>
+          <t>Accuray</t>
+        </is>
+      </c>
+      <c r="C412" s="5" t="inlineStr">
+        <is>
+          <t>https://accuray.wd5.myworkdayjobs.com/en-US/external/job/...</t>
+        </is>
+      </c>
+      <c r="D412" s="6" t="inlineStr">
+        <is>
+          <t>shortlisted</t>
+        </is>
+      </c>
+      <c r="E412" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="F412" s="4" t="inlineStr">
+        <is>
+          <t>The job is for a Data Science Intern, which is an internship role, so no experience gap deduction applies. The candidate has relevant skills in AI/ML and full stack development, but the job description does not explicitly mention any core tech stack mismatch. The candidate is enrolled in a Master of Computer Science, which is relevant to the role. However, the job is not in a non-tech company, finance/banking, or a pure software/AI/ML company, so no domain penalty applies. The candidate's role title does not exactly match the target roles, but it is close, so no role relevance bonus is added. The candidate requires sponsorship, which is a minor concern but not a significant auto-reject.</t>
+        </is>
+      </c>
+      <c r="G412" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-07T02:20:26.165774</t>
+        </is>
+      </c>
+      <c r="H412" s="7" t="inlineStr">
+        <is>
+          <t>➜ Apply</t>
+        </is>
+      </c>
+    </row>
+    <row r="413" ht="28" customHeight="1">
+      <c r="A413" s="8" t="inlineStr">
+        <is>
+          <t>Foundation Models for Autonomous Driving - AI Engineering Intern</t>
+        </is>
+      </c>
+      <c r="B413" s="9" t="inlineStr">
+        <is>
+          <t>Robert Bosch</t>
+        </is>
+      </c>
+      <c r="C413" s="10" t="inlineStr">
+        <is>
+          <t>https://jobs.smartrecruiters.com/BoschGroup/58dfbc1d-233b...</t>
+        </is>
+      </c>
+      <c r="D413" s="11" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="E413" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F413" s="9" t="inlineStr">
+        <is>
+          <t>Rejected: Found dealbreaker terms in JD (phd)</t>
+        </is>
+      </c>
+      <c r="G413" s="9" t="inlineStr">
+        <is>
+          <t>2026-03-07T02:20:26.165774</t>
+        </is>
+      </c>
+      <c r="H413" s="7" t="inlineStr">
+        <is>
+          <t>➜ Apply</t>
+        </is>
+      </c>
+    </row>
+    <row r="414" ht="28" customHeight="1">
+      <c r="A414" s="8" t="inlineStr">
+        <is>
+          <t>IT Data Science Intern (Business / Operations / Strategy)</t>
+        </is>
+      </c>
+      <c r="B414" s="9" t="inlineStr">
+        <is>
+          <t>Sandisk</t>
+        </is>
+      </c>
+      <c r="C414" s="10" t="inlineStr">
+        <is>
+          <t>https://jobs.smartrecruiters.com/Sandisk/89c7fb01-f845-4f...</t>
+        </is>
+      </c>
+      <c r="D414" s="11" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="E414" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F414" s="9" t="inlineStr">
+        <is>
+          <t>Rejected: Found dealbreaker terms in JD (phd)</t>
+        </is>
+      </c>
+      <c r="G414" s="9" t="inlineStr">
+        <is>
+          <t>2026-03-07T02:20:26.165774</t>
+        </is>
+      </c>
+      <c r="H414" s="7" t="inlineStr">
+        <is>
+          <t>➜ Apply</t>
+        </is>
+      </c>
+    </row>
+    <row r="415" ht="28" customHeight="1">
+      <c r="A415" s="3" t="inlineStr">
+        <is>
+          <t>Intern - AI and Analytics COE</t>
+        </is>
+      </c>
+      <c r="B415" s="4" t="inlineStr">
+        <is>
+          <t>Zayo</t>
+        </is>
+      </c>
+      <c r="C415" s="5" t="inlineStr">
+        <is>
+          <t>https://zayo.wd1.myworkdayjobs.com/en-US/zayo_careers/job...</t>
+        </is>
+      </c>
+      <c r="D415" s="6" t="inlineStr">
+        <is>
+          <t>shortlisted</t>
+        </is>
+      </c>
+      <c r="E415" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="F415" s="4" t="inlineStr">
+        <is>
+          <t>[SPONSORED] The job is explicitly for an Intern, which does not trigger the auto-reject. The candidate has relevant experience in Full Stack Development, AI Agents, LLM pipelines, Machine Learning, and Software Engineering, which aligns with the job requirements. The candidate's key skills in Python, Java, C++, TypeScript, JavaScript, and key AI/ML skills like PyTorch, TensorFlow, and scikit-learn are also relevant. However, the job is in the 'AI and Analytics COE' domain, which does not trigger a domain penalty. The candidate's preference for sponsorship (F-1 student, OPT/CPT or H1B) is not a factor in the score calculation.</t>
+        </is>
+      </c>
+      <c r="G415" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-07T02:20:26.165774</t>
+        </is>
+      </c>
+      <c r="H415" s="7" t="inlineStr">
+        <is>
+          <t>➜ Apply</t>
+        </is>
+      </c>
+    </row>
+    <row r="416" ht="28" customHeight="1">
+      <c r="A416" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineering Intern</t>
+        </is>
+      </c>
+      <c r="B416" s="4" t="inlineStr">
+        <is>
+          <t>T-Mobile</t>
+        </is>
+      </c>
+      <c r="C416" s="5" t="inlineStr">
+        <is>
+          <t>https://tmobile.wd1.myworkdayjobs.com/External/job/Overla...</t>
+        </is>
+      </c>
+      <c r="D416" s="6" t="inlineStr">
+        <is>
+          <t>shortlisted</t>
+        </is>
+      </c>
+      <c r="E416" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="F416" s="4" t="inlineStr">
+        <is>
+          <t>The job is for a Software Engineering Intern, which matches the candidate's preference for an internship role. The candidate has relevant skills in Full Stack Development, AI/ML, and Software Engineering, but the job does not explicitly require US Citizenship or a Security Clearance. The candidate is currently enrolled in a Master of Computer Science degree, which is a relevant educational background. There is no mention of a core tech stack mismatch, and the domain is in software engineering, which is not penalized. The candidate's experience level is appropriate for an internship, and there is no need for deep keyword weaving.</t>
+        </is>
+      </c>
+      <c r="G416" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-07T02:20:26.165774</t>
+        </is>
+      </c>
+      <c r="H416" s="7" t="inlineStr">
+        <is>
+          <t>➜ Apply</t>
+        </is>
+      </c>
+    </row>
+    <row r="417" ht="28" customHeight="1">
+      <c r="A417" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineer Intern</t>
+        </is>
+      </c>
+      <c r="B417" s="4" t="inlineStr">
+        <is>
+          <t>T-Mobile</t>
+        </is>
+      </c>
+      <c r="C417" s="5" t="inlineStr">
+        <is>
+          <t>https://tmobile.wd1.myworkdayjobs.com/External/job/Herndo...</t>
+        </is>
+      </c>
+      <c r="D417" s="6" t="inlineStr">
+        <is>
+          <t>shortlisted</t>
+        </is>
+      </c>
+      <c r="E417" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="F417" s="4" t="inlineStr">
+        <is>
+          <t>Auto-Shortlisted (Protected Title)</t>
+        </is>
+      </c>
+      <c r="G417" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-07T02:20:26.165774</t>
+        </is>
+      </c>
+      <c r="H417" s="7" t="inlineStr">
+        <is>
+          <t>➜ Apply</t>
+        </is>
+      </c>
+    </row>
+    <row r="418" ht="28" customHeight="1">
+      <c r="A418" s="8" t="inlineStr">
+        <is>
+          <t>Software Engineer Intern - Observability</t>
+        </is>
+      </c>
+      <c r="B418" s="9" t="inlineStr">
+        <is>
+          <t>Roku</t>
+        </is>
+      </c>
+      <c r="C418" s="10" t="inlineStr">
+        <is>
+          <t>https://www.weareroku.com/jobs/7687825?gh_jid=7687825</t>
+        </is>
+      </c>
+      <c r="D418" s="11" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="E418" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F418" s="9" t="inlineStr">
+        <is>
+          <t>Rejected: Non-US Location (Cardiff, UK)</t>
+        </is>
+      </c>
+      <c r="G418" s="9" t="inlineStr">
+        <is>
+          <t>2026-03-07T02:20:26.165774</t>
+        </is>
+      </c>
+      <c r="H418" s="7" t="inlineStr">
+        <is>
+          <t>➜ Apply</t>
+        </is>
+      </c>
+    </row>
+    <row r="419" ht="28" customHeight="1">
+      <c r="A419" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineering Intern - CUDA Build and Packaging</t>
+        </is>
+      </c>
+      <c r="B419" s="4" t="inlineStr">
+        <is>
+          <t>NVIDIA</t>
+        </is>
+      </c>
+      <c r="C419" s="5" t="inlineStr">
+        <is>
+          <t>https://nvidia.wd5.myworkdayjobs.com/NVIDIAExternalCareer...</t>
+        </is>
+      </c>
+      <c r="D419" s="6" t="inlineStr">
+        <is>
+          <t>shortlisted</t>
+        </is>
+      </c>
+      <c r="E419" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="F419" s="4" t="inlineStr">
+        <is>
+          <t>The job is for a Software Engineering Intern - CUDA Build and Packaging. The candidate is a Master's student and has relevant experience in Full Stack Development, AI Agents, LLM pipelines, and Machine Learning. The job does not explicitly require US Citizenship or a Security Clearance. The candidate is missing some core technologies like CUDA, but has experience in other relevant areas. The job is an internship, so there is no experience gap. The domain is in software engineering, so there is no domain penalty. The role title matches the candidate's target roles, so there is a role relevance bonus. The score is calculated as follows: 10 - 0 (auto-reject) - 0 (experience gap) - 1 (missing CUDA) + 1 (role relevance) = 9.</t>
+        </is>
+      </c>
+      <c r="G419" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-07T02:20:26.165774</t>
+        </is>
+      </c>
+      <c r="H419" s="7" t="inlineStr">
+        <is>
+          <t>➜ Apply</t>
+        </is>
+      </c>
+    </row>
+    <row r="420" ht="28" customHeight="1">
+      <c r="A420" s="3" t="inlineStr">
+        <is>
+          <t>AI Tech Analyst Intern</t>
+        </is>
+      </c>
+      <c r="B420" s="4" t="inlineStr">
+        <is>
+          <t>Precisely</t>
+        </is>
+      </c>
+      <c r="C420" s="5" t="inlineStr">
+        <is>
+          <t>https://www.precisely.com/careers-and-culture/us-jobs/job...</t>
+        </is>
+      </c>
+      <c r="D420" s="6" t="inlineStr">
+        <is>
+          <t>shortlisted</t>
+        </is>
+      </c>
+      <c r="E420" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="F420" s="4" t="inlineStr">
+        <is>
+          <t>The job is for an AI Tech Analyst Intern, which is an internship role, so no auto-reject occurs. The job does not explicitly require 3-4 years of experience, so no deduction for experience gap. The candidate has relevant skills in AI/ML, including PyTorch, TensorFlow, and NLP, which are not marked as required in the job description. The job is in the tech domain, so no domain penalty. The role title does not exactly match the candidate's target roles, but it involves AI/ML work, so a +1 bonus is applied. The candidate's visa status is F-1 student, OPT/CPT or H1B, which does not explicitly auto-reject the candidate. The final score is 7, which meets the candidate's score threshold of 6.</t>
+        </is>
+      </c>
+      <c r="G420" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-07T02:20:26.165774</t>
+        </is>
+      </c>
+      <c r="H420" s="7" t="inlineStr">
+        <is>
+          <t>➜ Apply</t>
+        </is>
+      </c>
+    </row>
+    <row r="421" ht="28" customHeight="1">
+      <c r="A421" s="3" t="inlineStr">
+        <is>
+          <t>CNN AI Innovation Intern</t>
+        </is>
+      </c>
+      <c r="B421" s="4" t="inlineStr">
+        <is>
+          <t>Warner Bros.</t>
+        </is>
+      </c>
+      <c r="C421" s="5" t="inlineStr">
+        <is>
+          <t>https://warnerbros.wd5.myworkdayjobs.com/global/job/NY-Ne...</t>
+        </is>
+      </c>
+      <c r="D421" s="6" t="inlineStr">
+        <is>
+          <t>shortlisted</t>
+        </is>
+      </c>
+      <c r="E421" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="F421" s="4" t="inlineStr">
+        <is>
+          <t>The job does not explicitly require US Citizenship or a Security Clearance, so no auto-reject occurs. The job is an internship, which does not require 3-4 or 5+ years of experience, so no experience gap deduction applies. The job does not mention any specific core technologies that the candidate is missing, so no core tech stack mismatch deduction applies. The domain is not finance, banking, or non-tech, so no domain penalty applies. The role title 'CNN AI Innovation Intern' matches the candidate's target roles, so a +1 role relevance bonus is applied. The candidate's score is 8, which meets the score threshold of 6.</t>
+        </is>
+      </c>
+      <c r="G421" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-07T02:20:26.165774</t>
+        </is>
+      </c>
+      <c r="H421" s="7" t="inlineStr">
+        <is>
+          <t>➜ Apply</t>
+        </is>
+      </c>
+    </row>
+    <row r="422" ht="28" customHeight="1">
+      <c r="A422" s="3" t="inlineStr">
+        <is>
+          <t>Systems Software Engineer Intern</t>
+        </is>
+      </c>
+      <c r="B422" s="4" t="inlineStr">
+        <is>
+          <t>Clockwork Systems</t>
+        </is>
+      </c>
+      <c r="C422" s="5" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/clockworksystems/jobs/58...</t>
+        </is>
+      </c>
+      <c r="D422" s="6" t="inlineStr">
+        <is>
+          <t>shortlisted</t>
+        </is>
+      </c>
+      <c r="E422" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="F422" s="4" t="inlineStr">
+        <is>
+          <t>Auto-Shortlisted (Protected Title)</t>
+        </is>
+      </c>
+      <c r="G422" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-07T02:20:26.165774</t>
+        </is>
+      </c>
+      <c r="H422" s="7" t="inlineStr">
+        <is>
+          <t>➜ Apply</t>
+        </is>
+      </c>
+    </row>
+    <row r="423" ht="28" customHeight="1">
+      <c r="A423" s="3" t="inlineStr">
+        <is>
+          <t>AI Solutions Consulting Intern</t>
+        </is>
+      </c>
+      <c r="B423" s="4" t="inlineStr">
+        <is>
+          <t>Withum</t>
+        </is>
+      </c>
+      <c r="C423" s="5" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/campusopportunities/jobs...</t>
+        </is>
+      </c>
+      <c r="D423" s="6" t="inlineStr">
+        <is>
+          <t>shortlisted</t>
+        </is>
+      </c>
+      <c r="E423" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="F423" s="4" t="inlineStr">
+        <is>
+          <t>The job is explicitly an internship, so it does not auto-reject. The candidate has relevant experience and skills, including Python, PyTorch, TensorFlow, and familiarity with Microsoft Office tools, which align with the job requirements. The job does not require 5+ years of experience, so no deduction applies here. There is no domain mismatch as the job is in AI solutions consulting, which aligns with the candidate's target roles. The candidate's experience level is consistent with the internship requirement. The job does not require US citizenship or security clearance, and the candidate's visa status is not an issue as no sponsorship is available. The candidate's role title does not match exactly, but it is close, and the job involves AI/ML work, which adds a bonus point.</t>
+        </is>
+      </c>
+      <c r="G423" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-07T02:20:26.165774</t>
+        </is>
+      </c>
+      <c r="H423" s="7" t="inlineStr">
+        <is>
+          <t>➜ Apply</t>
+        </is>
+      </c>
+    </row>
+    <row r="424" ht="28" customHeight="1">
+      <c r="A424" s="8" t="inlineStr">
+        <is>
+          <t>Research Scientist Intern - Applied Perception Science - PhD</t>
+        </is>
+      </c>
+      <c r="B424" s="9" t="inlineStr">
+        <is>
+          <t>Meta</t>
+        </is>
+      </c>
+      <c r="C424" s="10" t="inlineStr">
+        <is>
+          <t>https://www.metacareers.com/jobs/1884811572142821</t>
+        </is>
+      </c>
+      <c r="D424" s="11" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="E424" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F424" s="9" t="inlineStr">
+        <is>
+          <t>Rejected: Found dealbreaker terms in JD (phd)</t>
+        </is>
+      </c>
+      <c r="G424" s="9" t="inlineStr">
+        <is>
+          <t>2026-03-07T02:20:26.165774</t>
+        </is>
+      </c>
+      <c r="H424" s="7" t="inlineStr">
+        <is>
+          <t>➜ Apply</t>
+        </is>
+      </c>
+    </row>
+    <row r="425" ht="28" customHeight="1">
+      <c r="A425" s="3" t="inlineStr">
+        <is>
+          <t>AI &amp; Software Engineering Intern</t>
+        </is>
+      </c>
+      <c r="B425" s="4" t="inlineStr">
+        <is>
+          <t>USAFacts</t>
+        </is>
+      </c>
+      <c r="C425" s="5" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/usafacts/jobs/4173787009</t>
+        </is>
+      </c>
+      <c r="D425" s="6" t="inlineStr">
+        <is>
+          <t>shortlisted</t>
+        </is>
+      </c>
+      <c r="E425" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="F425" s="4" t="inlineStr">
+        <is>
+          <t>The job is for an AI &amp; Software Engineering Intern, which is an internship role, so no auto-reject occurs. The candidate is currently enrolled in a Master of Computer Science program, which aligns with the required educational background. The candidate has experience in Full Stack Development, Distributed Systems, AI Agents, LLM pipelines, Machine Learning, and Software Engineering, which aligns well with the job requirements. The candidate has strong programming skills in Python, JavaScript/TypeScript, and familiarity with databases and SQL, which are required. The candidate is interested in both software development and data systems, and has experience with AI/ML, which aligns with the job responsibilities. The candidate is open to relocation and remote work, which fits the job's flexible work model. The job does not explicitly require US Citizenship or Security Clearance, and the candidate does not require sponsorship, so no deductions apply. The job requires 3-4 years of experience, which deducts -2. There are no core tech stack mismatches, so no deductions apply. The job is in the tech domain, so no domain penalty applies. The role title matches the candidate's target roles, so a +1 is added. The final score is 8, which meets the candidate's score threshold of 6.</t>
+        </is>
+      </c>
+      <c r="G425" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-07T02:20:26.165774</t>
+        </is>
+      </c>
+      <c r="H425" s="7" t="inlineStr">
+        <is>
+          <t>➜ Apply</t>
+        </is>
+      </c>
+    </row>
+    <row r="426" ht="28" customHeight="1">
+      <c r="A426" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineer Intern</t>
+        </is>
+      </c>
+      <c r="B426" s="4" t="inlineStr">
+        <is>
+          <t>Genesis Therapeutics</t>
+        </is>
+      </c>
+      <c r="C426" s="5" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/genesis-therapeutics/ba13bf24-9c...</t>
+        </is>
+      </c>
+      <c r="D426" s="6" t="inlineStr">
+        <is>
+          <t>shortlisted</t>
+        </is>
+      </c>
+      <c r="E426" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="F426" s="4" t="inlineStr">
+        <is>
+          <t>Auto-Shortlisted (Protected Title)</t>
+        </is>
+      </c>
+      <c r="G426" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-07T02:20:26.165774</t>
+        </is>
+      </c>
+      <c r="H426" s="7" t="inlineStr">
+        <is>
+          <t>➜ Apply</t>
+        </is>
+      </c>
+    </row>
+    <row r="427" ht="28" customHeight="1">
+      <c r="A427" s="3" t="inlineStr">
+        <is>
+          <t>Intern - Software Engineer - Corporate and Business Services</t>
+        </is>
+      </c>
+      <c r="B427" s="4" t="inlineStr">
+        <is>
+          <t>Zebra Technologies</t>
+        </is>
+      </c>
+      <c r="C427" s="5" t="inlineStr">
+        <is>
+          <t>https://zebra.eightfold.ai/careers/job/343638073364</t>
+        </is>
+      </c>
+      <c r="D427" s="6" t="inlineStr">
+        <is>
+          <t>shortlisted</t>
+        </is>
+      </c>
+      <c r="E427" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="F427" s="4" t="inlineStr">
+        <is>
+          <t>The job is for a Software Engineer Intern and is located in Holtsville, NY, requiring at least 3 days of in-office attendance. The candidate is a Master's student and is enrolled in Computer Science, which meets the minimum qualifications. The job does not explicitly require US citizenship or a security clearance. The candidate has relevant skills in Full Stack Development, AI Agents, LLM pipelines, Machine Learning, and Software Engineering, which align well with the job requirements. However, the job is explicitly for an internship, so no deductions apply for experience. The job does not mention any specific core technologies that the candidate is missing, so no deductions apply for core tech stack mismatch. The job is in a tech company, so no domain penalty applies. The role title matches the candidate's target roles, so a +1 bonus is applied. The final score is 8, which meets the candidate's score threshold of 6.</t>
+        </is>
+      </c>
+      <c r="G427" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-07T02:20:26.165774</t>
+        </is>
+      </c>
+      <c r="H427" s="7" t="inlineStr">
+        <is>
+          <t>➜ Apply</t>
+        </is>
+      </c>
+    </row>
+    <row r="428" ht="28" customHeight="1">
+      <c r="A428" s="3" t="inlineStr">
+        <is>
+          <t>Software Developer Intern</t>
+        </is>
+      </c>
+      <c r="B428" s="4" t="inlineStr">
+        <is>
+          <t>SSOE Group</t>
+        </is>
+      </c>
+      <c r="C428" s="5" t="inlineStr">
+        <is>
+          <t>https://careers-ssoe.icims.com/jobs/3539/job?mobile=true&amp;...</t>
+        </is>
+      </c>
+      <c r="D428" s="6" t="inlineStr">
+        <is>
+          <t>shortlisted</t>
+        </is>
+      </c>
+      <c r="E428" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="F428" s="4" t="inlineStr">
+        <is>
+          <t>The job is explicitly for a Software Developer Intern, which matches the candidate's target roles. The job does not require US Citizenship or Security Clearance. The candidate is enrolled in a Master of Computer Science program, which meets the educational requirement. The job does not specify a required experience level, but it is an internship, which aligns with the candidate's preference. The job is not in a non-tech company, finance/banking, or a pure software/AI/ML company. The role does not explicitly involve AI/ML/LLM work, so no bonus is added. There are no core tech stack mismatches, as the candidate has experience with .NET, C#, and other relevant technologies. The job is in Toledo, Ohio, which is a specific location, but the candidate is open to relocation, so no penalty is applied.</t>
+        </is>
+      </c>
+      <c r="G428" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-07T02:20:26.165774</t>
+        </is>
+      </c>
+      <c r="H428" s="7" t="inlineStr">
+        <is>
+          <t>➜ Apply</t>
+        </is>
+      </c>
+    </row>
+    <row r="429" ht="28" customHeight="1">
+      <c r="A429" s="3" t="inlineStr">
+        <is>
+          <t>Data Analyst Intern</t>
+        </is>
+      </c>
+      <c r="B429" s="4" t="inlineStr">
+        <is>
+          <t>Hearst</t>
+        </is>
+      </c>
+      <c r="C429" s="5" t="inlineStr">
+        <is>
+          <t>https://eevd.fa.us6.oraclecloud.com/hcmUI/CandidateExperi...</t>
+        </is>
+      </c>
+      <c r="D429" s="6" t="inlineStr">
+        <is>
+          <t>shortlisted</t>
+        </is>
+      </c>
+      <c r="E429" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="F429" s="4" t="inlineStr">
+        <is>
+          <t>The job is for a Data Analyst Intern, which is an internship role, so no auto-reject occurs. The job does not explicitly require 3-4 years of experience, so no deduction for experience gap. The job does not mention any core tech stack mismatch, so no deduction for that. The job is in the data analytics domain, which is not a non-tech company, so no domain penalty. The role title does not match the candidate's target roles exactly, so no role relevance bonus. The candidate's visa status is not relevant to the job requirements.</t>
+        </is>
+      </c>
+      <c r="G429" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-07T02:20:26.165774</t>
+        </is>
+      </c>
+      <c r="H429" s="7" t="inlineStr">
+        <is>
+          <t>➜ Apply</t>
+        </is>
+      </c>
+    </row>
+    <row r="430" ht="28" customHeight="1">
+      <c r="A430" s="3" t="inlineStr">
+        <is>
+          <t>Physical AI Intern</t>
+        </is>
+      </c>
+      <c r="B430" s="4" t="inlineStr">
+        <is>
+          <t>Keysight Technologies</t>
+        </is>
+      </c>
+      <c r="C430" s="5" t="inlineStr">
+        <is>
+          <t>https://jobs.keysight.com/jobs/51866?lang=en-us&amp;icims=1</t>
+        </is>
+      </c>
+      <c r="D430" s="6" t="inlineStr">
+        <is>
+          <t>shortlisted</t>
+        </is>
+      </c>
+      <c r="E430" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="F430" s="4" t="inlineStr">
+        <is>
+          <t>Auto-Shortlisted (Protected Title)</t>
+        </is>
+      </c>
+      <c r="G430" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-07T02:20:26.165774</t>
+        </is>
+      </c>
+      <c r="H430" s="7" t="inlineStr">
+        <is>
+          <t>➜ Apply</t>
+        </is>
+      </c>
+    </row>
+    <row r="431" ht="28" customHeight="1">
+      <c r="A431" s="8" t="inlineStr">
+        <is>
+          <t>ML Intern – Calibration &amp; Measurement Optimization</t>
+        </is>
+      </c>
+      <c r="B431" s="9" t="inlineStr">
+        <is>
+          <t>Keysight Technologies</t>
+        </is>
+      </c>
+      <c r="C431" s="10" t="inlineStr">
+        <is>
+          <t>https://jobs.keysight.com/jobs/51868?lang=en-us&amp;icims=1</t>
+        </is>
+      </c>
+      <c r="D431" s="11" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="E431" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F431" s="9" t="inlineStr">
+        <is>
+          <t>Rejected: Found dealbreaker terms in JD (phd)</t>
+        </is>
+      </c>
+      <c r="G431" s="9" t="inlineStr">
+        <is>
+          <t>2026-03-07T02:20:26.165774</t>
+        </is>
+      </c>
+      <c r="H431" s="7" t="inlineStr">
+        <is>
+          <t>➜ Apply</t>
+        </is>
+      </c>
+    </row>
+    <row r="432" ht="28" customHeight="1">
+      <c r="A432" s="3" t="inlineStr">
+        <is>
+          <t>Student Engineering Software</t>
+        </is>
+      </c>
+      <c r="B432" s="4" t="inlineStr">
+        <is>
+          <t>Magna International</t>
+        </is>
+      </c>
+      <c r="C432" s="5" t="inlineStr">
+        <is>
+          <t>https://magna.wd3.myworkdayjobs.com/Magna/job/Lowell-Mass...</t>
+        </is>
+      </c>
+      <c r="D432" s="6" t="inlineStr">
+        <is>
+          <t>shortlisted</t>
+        </is>
+      </c>
+      <c r="E432" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="F432" s="4" t="inlineStr">
+        <is>
+          <t>The job does not explicitly require US Citizenship or Security Clearance, so no auto-reject. The job is for an internship, which does not require 3-4 or 5+ years of experience, so no experience gap deduction. The job does not mention any specific core technologies that the candidate is missing, so no core tech stack mismatch deduction. The job is in the software engineering domain, so no domain penalty. The role title does not exactly match the candidate's target roles, but it involves software engineering work, so no role relevance bonus. The candidate's visa status is not relevant to the score calculation.</t>
+        </is>
+      </c>
+      <c r="G432" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-07T02:20:26.165774</t>
+        </is>
+      </c>
+      <c r="H432" s="7" t="inlineStr">
+        <is>
+          <t>➜ Apply</t>
+        </is>
+      </c>
+    </row>
+    <row r="433" ht="28" customHeight="1">
+      <c r="A433" s="8" t="inlineStr">
+        <is>
+          <t>Student – Data Scientist</t>
+        </is>
+      </c>
+      <c r="B433" s="9" t="inlineStr">
+        <is>
+          <t>Sun Life</t>
+        </is>
+      </c>
+      <c r="C433" s="10" t="inlineStr">
+        <is>
+          <t>https://sunlife.wd3.myworkdayjobs.com/en-US/Campus/job/To...</t>
+        </is>
+      </c>
+      <c r="D433" s="11" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="E433" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F433" s="9" t="inlineStr">
+        <is>
+          <t>Rejected: Non-US Location (Toronto, ON, Canada)</t>
+        </is>
+      </c>
+      <c r="G433" s="9" t="inlineStr">
+        <is>
+          <t>2026-03-07T02:20:26.165774</t>
+        </is>
+      </c>
+      <c r="H433" s="7" t="inlineStr">
+        <is>
+          <t>➜ Apply</t>
+        </is>
+      </c>
+    </row>
+    <row r="434" ht="28" customHeight="1">
+      <c r="A434" s="8" t="inlineStr">
+        <is>
+          <t>Backend Engineer Intern</t>
+        </is>
+      </c>
+      <c r="B434" s="9" t="inlineStr">
+        <is>
+          <t>Proofpoint</t>
+        </is>
+      </c>
+      <c r="C434" s="10" t="inlineStr">
+        <is>
+          <t>https://proofpoint.wd5.myworkdayjobs.com/proofpointcareer...</t>
+        </is>
+      </c>
+      <c r="D434" s="11" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="E434" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F434" s="9" t="inlineStr">
+        <is>
+          <t>Rejected: Non-US Location (Belfast, UK)</t>
+        </is>
+      </c>
+      <c r="G434" s="9" t="inlineStr">
+        <is>
+          <t>2026-03-07T02:20:26.165774</t>
+        </is>
+      </c>
+      <c r="H434" s="7" t="inlineStr">
+        <is>
+          <t>➜ Apply</t>
+        </is>
+      </c>
+    </row>
+    <row r="435" ht="28" customHeight="1">
+      <c r="A435" s="8" t="inlineStr">
+        <is>
+          <t>Compiler Engineering Intern - Performance Tracking and Analysis</t>
+        </is>
+      </c>
+      <c r="B435" s="9" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="C435" s="10" t="inlineStr">
+        <is>
+          <t>https://intel.wd1.myworkdayjobs.com/en-us/external/job/Ca...</t>
+        </is>
+      </c>
+      <c r="D435" s="11" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="E435" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F435" s="9" t="inlineStr">
+        <is>
+          <t>Rejected: Non-US Location (Toronto, ON, Canada)</t>
+        </is>
+      </c>
+      <c r="G435" s="9" t="inlineStr">
+        <is>
+          <t>2026-03-07T02:20:26.165774</t>
+        </is>
+      </c>
+      <c r="H435" s="7" t="inlineStr">
+        <is>
+          <t>➜ Apply</t>
+        </is>
+      </c>
+    </row>
+    <row r="436" ht="28" customHeight="1">
+      <c r="A436" s="3" t="inlineStr">
+        <is>
+          <t>Mainstream SBU Intern</t>
+        </is>
+      </c>
+      <c r="B436" s="4" t="inlineStr">
+        <is>
+          <t>Entegris</t>
+        </is>
+      </c>
+      <c r="C436" s="5" t="inlineStr">
+        <is>
+          <t>https://entegris.wd1.myworkdayjobs.com/entegriscareers/jo...</t>
+        </is>
+      </c>
+      <c r="D436" s="6" t="inlineStr">
+        <is>
+          <t>shortlisted</t>
+        </is>
+      </c>
+      <c r="E436" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="F436" s="4" t="inlineStr">
+        <is>
+          <t>The job does not explicitly require US Citizenship or Security Clearance, so no auto-reject. The job is an internship, which does not require 3-4 or 5+ years of experience, so no experience gap deduction. The job does not mention any specific core technologies that the candidate is missing, so no core tech stack mismatch deduction. The job is in the tech domain, so no domain penalty. The role title does not exactly match the candidate's target roles, so no role relevance bonus. The candidate's visa status is a preference, not a requirement, so no score deduction for that. The candidate's score is 10, which meets the score threshold of 6.</t>
+        </is>
+      </c>
+      <c r="G436" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-07T02:20:26.165774</t>
+        </is>
+      </c>
+      <c r="H436" s="7" t="inlineStr">
+        <is>
+          <t>➜ Apply</t>
+        </is>
+      </c>
+    </row>
+    <row r="437" ht="28" customHeight="1">
+      <c r="A437" s="3" t="inlineStr">
+        <is>
+          <t>Applied Science Intern</t>
+        </is>
+      </c>
+      <c r="B437" s="4" t="inlineStr">
+        <is>
+          <t>Relativity</t>
+        </is>
+      </c>
+      <c r="C437" s="5" t="inlineStr">
+        <is>
+          <t>https://kcura.wd1.myworkdayjobs.com/en-US/External_Career...</t>
+        </is>
+      </c>
+      <c r="D437" s="6" t="inlineStr">
+        <is>
+          <t>shortlisted</t>
+        </is>
+      </c>
+      <c r="E437" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="F437" s="4" t="inlineStr">
+        <is>
+          <t>The job does not explicitly require US Citizenship or Security Clearance, so no auto-reject. The job is an internship, so no experience gap deduction. The job does not mention any specific core tech stack that the candidate is missing, so no core tech stack mismatch deduction. The job is in the tech domain, so no domain penalty. The role title 'Applied Science Intern' matches the candidate's target roles, so a +1 is added. The candidate's score is 8, which is above the threshold of 6, so no further adjustments are needed.</t>
+        </is>
+      </c>
+      <c r="G437" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-07T02:20:26.165774</t>
+        </is>
+      </c>
+      <c r="H437" s="7" t="inlineStr">
+        <is>
+          <t>➜ Apply</t>
+        </is>
+      </c>
+    </row>
+    <row r="438" ht="28" customHeight="1">
+      <c r="A438" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineer – Community Apprenticeship</t>
+        </is>
+      </c>
+      <c r="B438" s="4" t="inlineStr">
+        <is>
+          <t>Roblox</t>
+        </is>
+      </c>
+      <c r="C438" s="5" t="inlineStr">
+        <is>
+          <t>https://careers.roblox.com/jobs/7654991?gh_jid=7654991</t>
+        </is>
+      </c>
+      <c r="D438" s="6" t="inlineStr">
+        <is>
+          <t>shortlisted</t>
+        </is>
+      </c>
+      <c r="E438" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="F438" s="4" t="inlineStr">
+        <is>
+          <t>Starting at 10/10. No auto-rejects apply. Experience gap: The job does not explicitly require 3-4 or 5+ years of experience, so no deduction. Core tech stack mismatch: The candidate is missing Lua/Luau, which is a required technology. Domain penalty: The job is in the tech domain, so no penalty. Role relevance bonus: The role title does not match the candidate's target roles exactly, so no bonus. Final score: 8 - 1 = 7.</t>
+        </is>
+      </c>
+      <c r="G438" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-07T02:20:26.165774</t>
+        </is>
+      </c>
+      <c r="H438" s="7" t="inlineStr">
+        <is>
+          <t>➜ Apply</t>
+        </is>
+      </c>
+    </row>
+    <row r="439" ht="28" customHeight="1">
+      <c r="A439" s="3" t="inlineStr">
+        <is>
+          <t>AI Innovation Scholar</t>
+        </is>
+      </c>
+      <c r="B439" s="4" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C439" s="5" t="inlineStr">
+        <is>
+          <t>https://apply.deloitte.com/en_US/careers/JobDetail/Deloit...</t>
+        </is>
+      </c>
+      <c r="D439" s="6" t="inlineStr">
+        <is>
+          <t>shortlisted</t>
+        </is>
+      </c>
+      <c r="E439" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="F439" s="4" t="inlineStr">
+        <is>
+          <t>Auto-reject: The job does not explicitly require US Citizenship or Security Clearance, and it is not a senior/managerial level position. The job requires 3-4 years of experience, which deducts -2. The job is in the AI domain, which does not apply the domain penalty. The role title does not exactly match the candidate's target roles, but it involves AI/ML work, which adds +1. The candidate's experience and skills align well with the job requirements, but the job does not explicitly require 5+ years of experience, so no further deductions apply.</t>
+        </is>
+      </c>
+      <c r="G439" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-07T02:20:26.165774</t>
+        </is>
+      </c>
+      <c r="H439" s="7" t="inlineStr">
+        <is>
+          <t>➜ Apply</t>
+        </is>
+      </c>
+    </row>
+    <row r="440" ht="28" customHeight="1">
+      <c r="A440" s="8" t="inlineStr">
+        <is>
+          <t>Intern – AI Implementation</t>
+        </is>
+      </c>
+      <c r="B440" s="9" t="inlineStr">
+        <is>
+          <t>Scout Motors</t>
+        </is>
+      </c>
+      <c r="C440" s="10" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/scoutmotors/jobs/5072662007</t>
+        </is>
+      </c>
+      <c r="D440" s="11" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="E440" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F440" s="9" t="inlineStr">
+        <is>
+          <t>The job is explicitly for an Intern, so it auto-rejects at STEP 1. The candidate is enrolled in a Master's program, which is not a Bachelor's degree as required by the job. There are no core tech stack mismatches, and the domain is not non-tech. The candidate's role title does not match exactly, but the job is an internship, so this is not a significant penalty. The candidate's visa status is not relevant as the job does not require sponsorship.</t>
+        </is>
+      </c>
+      <c r="G440" s="9" t="inlineStr">
+        <is>
+          <t>2026-03-07T02:20:26.165774</t>
+        </is>
+      </c>
+      <c r="H440" s="7" t="inlineStr">
+        <is>
+          <t>➜ Apply</t>
+        </is>
+      </c>
+    </row>
+    <row r="441" ht="28" customHeight="1">
+      <c r="A441" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineering Intern - Data Engineer</t>
+        </is>
+      </c>
+      <c r="B441" s="4" t="inlineStr">
+        <is>
+          <t>Calix</t>
+        </is>
+      </c>
+      <c r="C441" s="5" t="inlineStr">
+        <is>
+          <t>https://calix.wd1.myworkdayjobs.com/External/job/Remote--...</t>
+        </is>
+      </c>
+      <c r="D441" s="6" t="inlineStr">
+        <is>
+          <t>shortlisted</t>
+        </is>
+      </c>
+      <c r="E441" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="F441" s="4" t="inlineStr">
+        <is>
+          <t>The job is for a Software Engineering Intern - Data Engineer, which is an internship role, so no auto-reject occurs. The candidate has relevant experience in Full Stack Development, AI Agents, LLM pipelines, Machine Learning, and Software Engineering, which aligns with the core tech stack. The candidate's skills in Python, Java, C++, TypeScript, JavaScript, and key AI/ML tools like PyTorch and TensorFlow are relevant. The job does not explicitly require US Citizenship or Security Clearance, and it is an internship, so no experience gap penalty applies. The domain is in software engineering, so no domain penalty applies. The role title does not exactly match the candidate's target roles, but it is relevant, so no role relevance bonus is added.</t>
+        </is>
+      </c>
+      <c r="G441" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-07T02:20:26.165774</t>
+        </is>
+      </c>
+      <c r="H441" s="7" t="inlineStr">
+        <is>
+          <t>➜ Apply</t>
+        </is>
+      </c>
+    </row>
+    <row r="442" ht="28" customHeight="1">
+      <c r="A442" s="3" t="inlineStr">
+        <is>
+          <t>Python Developer Intern</t>
+        </is>
+      </c>
+      <c r="B442" s="4" t="inlineStr">
+        <is>
+          <t>Precisely</t>
+        </is>
+      </c>
+      <c r="C442" s="5" t="inlineStr">
+        <is>
+          <t>https://www.precisely.com/careers-and-culture/us-jobs/job...</t>
+        </is>
+      </c>
+      <c r="D442" s="6" t="inlineStr">
+        <is>
+          <t>shortlisted</t>
+        </is>
+      </c>
+      <c r="E442" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="F442" s="4" t="inlineStr">
+        <is>
+          <t>The job is for a Python Developer Intern, which is an internship level position, so no auto-reject occurs. The job does not explicitly require US Citizenship or Security Clearance. The candidate has 3-4 years of experience, so no deduction for experience gap. The job does not mention any specific core tech stack requirements, so no deduction for core tech stack mismatch. The domain is in data integrity and AI, which is relevant to the candidate's skills, so no domain penalty. The role title does not exactly match the candidate's target roles, but it is close, so no role relevance bonus. The candidate's score is 10, which meets the score threshold of 6.</t>
+        </is>
+      </c>
+      <c r="G442" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-07T02:20:26.165774</t>
+        </is>
+      </c>
+      <c r="H442" s="7" t="inlineStr">
+        <is>
+          <t>➜ Apply</t>
+        </is>
+      </c>
+    </row>
+    <row r="443" ht="28" customHeight="1">
+      <c r="A443" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineering Intern</t>
+        </is>
+      </c>
+      <c r="B443" s="4" t="inlineStr">
+        <is>
+          <t>Precisely</t>
+        </is>
+      </c>
+      <c r="C443" s="5" t="inlineStr">
+        <is>
+          <t>https://www.precisely.com/careers-and-culture/us-jobs/job...</t>
+        </is>
+      </c>
+      <c r="D443" s="6" t="inlineStr">
+        <is>
+          <t>shortlisted</t>
+        </is>
+      </c>
+      <c r="E443" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="F443" s="4" t="inlineStr">
+        <is>
+          <t>The job is for a Software Engineering Intern, which does not auto-reject the candidate based on experience level. The candidate has relevant skills in Full Stack Development, AI Agents, LLM pipelines, Machine Learning, and Software Engineering, which aligns with the job requirements. The candidate is missing some core technologies like React, Next.js, and Node.js, which are not explicitly required but are preferred. There is no domain penalty as the job is in the software engineering domain. The candidate's role title is a close match to the job title, and the score is above the threshold of 6.</t>
+        </is>
+      </c>
+      <c r="G443" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-07T02:20:26.165774</t>
+        </is>
+      </c>
+      <c r="H443" s="7" t="inlineStr">
+        <is>
+          <t>➜ Apply</t>
+        </is>
+      </c>
+    </row>
+    <row r="444" ht="28" customHeight="1">
+      <c r="A444" s="3" t="inlineStr">
+        <is>
+          <t>Engineering Intern</t>
+        </is>
+      </c>
+      <c r="B444" s="4" t="inlineStr">
+        <is>
+          <t>Hendrick Motorsports</t>
+        </is>
+      </c>
+      <c r="C444" s="5" t="inlineStr">
+        <is>
+          <t>https://hendrick.wd5.myworkdayjobs.com/HMSCareers/job/Hen...</t>
+        </is>
+      </c>
+      <c r="D444" s="6" t="inlineStr">
+        <is>
+          <t>shortlisted</t>
+        </is>
+      </c>
+      <c r="E444" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="F444" s="4" t="inlineStr">
+        <is>
+          <t>The job is for an Engineering Intern, which is an internship level position, so no auto-reject occurs. The job does not explicitly require US Citizenship or Security Clearance. The candidate has relevant experience in Full Stack Development, AI Agents, LLM pipelines, Machine Learning, and Software Engineering, which aligns with the core tech stack required for the role. The job is in the automotive industry, which is not a non-tech company, so no domain penalty applies. The candidate's target roles include Intern roles, which match the job title exactly, providing a +1 bonus. The candidate's skills and experience are well-aligned with the job requirements, and the score is above the threshold of 6.</t>
+        </is>
+      </c>
+      <c r="G444" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-07T02:20:26.165774</t>
+        </is>
+      </c>
+      <c r="H444" s="7" t="inlineStr">
+        <is>
+          <t>➜ Apply</t>
+        </is>
+      </c>
+    </row>
+    <row r="445" ht="28" customHeight="1">
+      <c r="A445" s="3" t="inlineStr">
+        <is>
+          <t>Student Engineering Software</t>
+        </is>
+      </c>
+      <c r="B445" s="4" t="inlineStr">
+        <is>
+          <t>Magna</t>
+        </is>
+      </c>
+      <c r="C445" s="5" t="inlineStr">
+        <is>
+          <t>https://wd3.myworkdaysite.com/recruiting/magna/Magna/job/...</t>
+        </is>
+      </c>
+      <c r="D445" s="6" t="inlineStr">
+        <is>
+          <t>shortlisted</t>
+        </is>
+      </c>
+      <c r="E445" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="F445" s="4" t="inlineStr">
+        <is>
+          <t>The job does not explicitly require US Citizenship or a Security Clearance, so no auto-reject applies. The job is for an internship, which does not require 3-4 or 5+ years of experience, so no experience gap deductions apply. The job does not mention any specific core technologies that the candidate is missing, so no core tech stack mismatch deductions apply. The job is in the software engineering domain, so no domain penalty applies. The role title does not exactly match the candidate's target roles, but it involves software engineering work, so a +1 role relevance bonus is applied. The candidate's visa status is not a factor since the job does not explicitly require US Citizenship or a Security Clearance.</t>
+        </is>
+      </c>
+      <c r="G445" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-07T02:20:26.165774</t>
+        </is>
+      </c>
+      <c r="H445" s="7" t="inlineStr">
+        <is>
+          <t>➜ Apply</t>
+        </is>
+      </c>
+    </row>
+    <row r="446" ht="28" customHeight="1">
+      <c r="A446" s="3" t="inlineStr">
+        <is>
+          <t>Research Intern on Generative and Protective AI for Content Creation</t>
+        </is>
+      </c>
+      <c r="B446" s="4" t="inlineStr">
+        <is>
+          <t>Sony</t>
+        </is>
+      </c>
+      <c r="C446" s="5" t="inlineStr">
+        <is>
+          <t>https://sonyglobal.wd1.myworkdayjobs.com/SonyGlobalCareer...</t>
+        </is>
+      </c>
+      <c r="D446" s="6" t="inlineStr">
+        <is>
+          <t>shortlisted</t>
+        </is>
+      </c>
+      <c r="E446" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="F446" s="4" t="inlineStr">
+        <is>
+          <t>The job does not explicitly require US Citizenship or Security Clearance, so no auto-reject applies. The job requires 3-4 years of experience, which deducts -2. The job is in the AI/ML domain, which does not apply the -4 penalty. The candidate's experience and skills align well with the job requirements, so no core tech stack mismatch penalty applies. The role title does not exactly match the candidate's target roles, but it involves AI/ML work, which adds +1. The candidate's visa status is a preference, not a requirement, so no penalty is applied here.</t>
+        </is>
+      </c>
+      <c r="G446" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-07T02:20:26.165774</t>
+        </is>
+      </c>
+      <c r="H446" s="7" t="inlineStr">
+        <is>
+          <t>➜ Apply</t>
+        </is>
+      </c>
+    </row>
+    <row r="447" ht="28" customHeight="1">
+      <c r="A447" s="3" t="inlineStr">
+        <is>
+          <t>Data Analyst / BI Developer Intern</t>
+        </is>
+      </c>
+      <c r="B447" s="4" t="inlineStr">
+        <is>
+          <t>CACI</t>
+        </is>
+      </c>
+      <c r="C447" s="5" t="inlineStr">
+        <is>
+          <t>https://caci.wd1.myworkdayjobs.com/external/job/US-VA-Arl...</t>
+        </is>
+      </c>
+      <c r="D447" s="6" t="inlineStr">
+        <is>
+          <t>shortlisted</t>
+        </is>
+      </c>
+      <c r="E447" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="F447" s="4" t="inlineStr">
+        <is>
+          <t>The job title is 'Data Analyst / BI Developer Intern', which is an internship role, so no experience gap deduction applies. The job does not explicitly require US Citizenship or Security Clearance, and it is an internship role, so no auto-rejects apply. There are no core tech stack mismatches as the candidate has experience with Python, SQL, and other relevant technologies. The job is not in a domain that incurs a penalty. The role title does not match the candidate's target roles exactly, so no role relevance bonus applies.</t>
+        </is>
+      </c>
+      <c r="G447" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-07T02:20:26.165774</t>
+        </is>
+      </c>
+      <c r="H447" s="7" t="inlineStr">
+        <is>
+          <t>➜ Apply</t>
+        </is>
+      </c>
+    </row>
+    <row r="448" ht="28" customHeight="1">
+      <c r="A448" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineer Intern</t>
+        </is>
+      </c>
+      <c r="B448" s="4" t="inlineStr">
+        <is>
+          <t>Leidos</t>
+        </is>
+      </c>
+      <c r="C448" s="5" t="inlineStr">
+        <is>
+          <t>https://leidos.wd5.myworkdayjobs.com/External/job/Oklahom...</t>
+        </is>
+      </c>
+      <c r="D448" s="6" t="inlineStr">
+        <is>
+          <t>shortlisted</t>
+        </is>
+      </c>
+      <c r="E448" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="F448" s="4" t="inlineStr">
+        <is>
+          <t>Auto-Shortlisted (Protected Title)</t>
+        </is>
+      </c>
+      <c r="G448" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-07T02:20:26.165774</t>
+        </is>
+      </c>
+      <c r="H448" s="7" t="inlineStr">
+        <is>
+          <t>➜ Apply</t>
+        </is>
+      </c>
+    </row>
+    <row r="449" ht="28" customHeight="1">
+      <c r="A449" s="8" t="inlineStr">
+        <is>
+          <t>AI/ML Intern</t>
+        </is>
+      </c>
+      <c r="B449" s="9" t="inlineStr">
+        <is>
+          <t>Applied Materials</t>
+        </is>
+      </c>
+      <c r="C449" s="10" t="inlineStr">
+        <is>
+          <t>https://amat.wd1.myworkdayjobs.com/External/job/Santa-Cla...</t>
+        </is>
+      </c>
+      <c r="D449" s="11" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="E449" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F449" s="9" t="inlineStr">
+        <is>
+          <t>Scrape failed to find JD text</t>
+        </is>
+      </c>
+      <c r="G449" s="9" t="inlineStr">
+        <is>
+          <t>2026-03-07T02:20:26.166785</t>
+        </is>
+      </c>
+      <c r="H449" s="7" t="inlineStr">
+        <is>
+          <t>➜ Apply</t>
+        </is>
+      </c>
+    </row>
+    <row r="450" ht="28" customHeight="1">
+      <c r="A450" s="3" t="inlineStr">
+        <is>
+          <t>Intern - AI Automation</t>
+        </is>
+      </c>
+      <c r="B450" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">S&amp;P Global </t>
+        </is>
+      </c>
+      <c r="C450" s="5" t="inlineStr">
+        <is>
+          <t>https://spgi.wd5.myworkdayjobs.com/en-US/SPGI_Careers/job...</t>
+        </is>
+      </c>
+      <c r="D450" s="6" t="inlineStr">
+        <is>
+          <t>shortlisted</t>
+        </is>
+      </c>
+      <c r="E450" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="F450" s="4" t="inlineStr">
+        <is>
+          <t>The job does not explicitly require US Citizenship or Security Clearance, so no auto-reject. The job is an Internship, so no experience gap deduction. The candidate has experience in AI Agents, LLM pipelines, and Machine Learning, which are core technologies required for the job. The job is in the finance domain, which is not a domain penalty. The role title does not exactly match the candidate's target roles, but it involves AI/ML work, so a +1 is added. The candidate's visa status is a preference, not a requirement, so no deduction is applied here.</t>
+        </is>
+      </c>
+      <c r="G450" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-07T02:20:26.166785</t>
+        </is>
+      </c>
+      <c r="H450" s="7" t="inlineStr">
+        <is>
+          <t>➜ Apply</t>
+        </is>
+      </c>
+    </row>
+    <row r="451" ht="28" customHeight="1">
+      <c r="A451" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineer Intern - Svt Team</t>
+        </is>
+      </c>
+      <c r="B451" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> CCC Intelligent Solutions</t>
+        </is>
+      </c>
+      <c r="C451" s="5" t="inlineStr">
+        <is>
+          <t>https://cccis.wd1.myworkdayjobs.com/broadbean_external/jo...</t>
+        </is>
+      </c>
+      <c r="D451" s="6" t="inlineStr">
+        <is>
+          <t>shortlisted</t>
+        </is>
+      </c>
+      <c r="E451" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="F451" s="4" t="inlineStr">
+        <is>
+          <t>Auto-Shortlisted (Protected Title)</t>
+        </is>
+      </c>
+      <c r="G451" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-07T02:20:26.166785</t>
+        </is>
+      </c>
+      <c r="H451" s="7" t="inlineStr">
+        <is>
+          <t>➜ Apply</t>
+        </is>
+      </c>
+    </row>
+    <row r="452" ht="28" customHeight="1">
+      <c r="A452" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineer Intern</t>
+        </is>
+      </c>
+      <c r="B452" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> CCC Intelligent Solutions</t>
+        </is>
+      </c>
+      <c r="C452" s="5" t="inlineStr">
+        <is>
+          <t>https://cccis.wd1.myworkdayjobs.com/broadbean_external/jo...</t>
+        </is>
+      </c>
+      <c r="D452" s="6" t="inlineStr">
+        <is>
+          <t>shortlisted</t>
+        </is>
+      </c>
+      <c r="E452" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="F452" s="4" t="inlineStr">
+        <is>
+          <t>Auto-Shortlisted (Protected Title)</t>
+        </is>
+      </c>
+      <c r="G452" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-07T02:20:26.166785</t>
+        </is>
+      </c>
+      <c r="H452" s="7" t="inlineStr">
+        <is>
+          <t>➜ Apply</t>
+        </is>
+      </c>
+    </row>
+    <row r="453" ht="28" customHeight="1">
+      <c r="A453" s="8" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer – Co-op/Intern</t>
+        </is>
+      </c>
+      <c r="B453" s="9" t="inlineStr">
+        <is>
+          <t>Bank of Montreal</t>
+        </is>
+      </c>
+      <c r="C453" s="10" t="inlineStr">
+        <is>
+          <t>https://bmo.wd3.myworkdayjobs.com/Privileged/job/Toronto-...</t>
+        </is>
+      </c>
+      <c r="D453" s="11" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="E453" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F453" s="9" t="inlineStr">
+        <is>
+          <t>Rejected: Non-US Location (Toronto, ON, Canada)</t>
+        </is>
+      </c>
+      <c r="G453" s="9" t="inlineStr">
+        <is>
+          <t>2026-03-07T02:20:26.166785</t>
+        </is>
+      </c>
+      <c r="H453" s="7" t="inlineStr">
+        <is>
+          <t>➜ Apply</t>
+        </is>
+      </c>
+    </row>
+    <row r="454" ht="28" customHeight="1">
+      <c r="A454" s="3" t="inlineStr">
+        <is>
+          <t>Data &amp; Research Intern</t>
+        </is>
+      </c>
+      <c r="B454" s="4" t="inlineStr">
+        <is>
+          <t>Vevo</t>
+        </is>
+      </c>
+      <c r="C454" s="5" t="inlineStr">
+        <is>
+          <t>https://jobs.lever.co/vevo/61911ba3-e8d7-4369-bc96-c47e5f...</t>
+        </is>
+      </c>
+      <c r="D454" s="6" t="inlineStr">
+        <is>
+          <t>shortlisted</t>
+        </is>
+      </c>
+      <c r="E454" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="F454" s="4" t="inlineStr">
+        <is>
+          <t>The job is for a Data &amp; Research Intern, which is an internship role, so no auto-reject occurs. The job does not explicitly require 3-4 years of experience, so no deduction for experience gap. The candidate has relevant skills in AI and machine learning, but the job description does not explicitly list these as required. There is no domain penalty since the job is in data science, which is related to the candidate's skills. The role title does not match the candidate's target roles exactly, so no bonus is added. The score is 7, which meets the candidate's score threshold of 6.</t>
+        </is>
+      </c>
+      <c r="G454" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-07T02:20:26.166785</t>
+        </is>
+      </c>
+      <c r="H454" s="7" t="inlineStr">
+        <is>
+          <t>➜ Apply</t>
+        </is>
+      </c>
+    </row>
+    <row r="455" ht="28" customHeight="1">
+      <c r="A455" s="3" t="inlineStr">
+        <is>
+          <t>Special Executions – Data Analytics Analyst</t>
+        </is>
+      </c>
+      <c r="B455" s="4" t="inlineStr">
+        <is>
+          <t>Financial Technology Partners</t>
+        </is>
+      </c>
+      <c r="C455" s="5" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/financialtechnologypartn...</t>
+        </is>
+      </c>
+      <c r="D455" s="6" t="inlineStr">
+        <is>
+          <t>shortlisted</t>
+        </is>
+      </c>
+      <c r="E455" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="F455" s="4" t="inlineStr">
+        <is>
+          <t>The job is explicitly for a Data Analytics Summer Analyst role, which is an internship. The candidate is currently enrolled in a Master of Computer Science program and has relevant skills in Full Stack Development, AI Agents, LLM pipelines, Machine Learning, and Software Engineering. The job requires a minimum 3.6 GPA and specific tools like SQL, Python, and Tableau, which the candidate has. However, the job does not explicitly require US Citizenship or Security Clearance, and it is not a senior-level position. The job is in the financial technology sector, which is not a non-tech company. The candidate's experience level is consistent with an intern, and the role involves data analytics, which aligns with the candidate's preferences. The candidate's visa status is a requirement for sponsorship, but the job does not mention sponsorship. The candidate's skills and experience match the job requirements closely, and there are no significant gaps or domain mismatches.</t>
+        </is>
+      </c>
+      <c r="G455" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-07T02:20:26.166785</t>
+        </is>
+      </c>
+      <c r="H455" s="7" t="inlineStr">
+        <is>
+          <t>➜ Apply</t>
+        </is>
+      </c>
+    </row>
+    <row r="456" ht="28" customHeight="1">
+      <c r="A456" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineer Intern</t>
+        </is>
+      </c>
+      <c r="B456" s="4" t="inlineStr">
+        <is>
+          <t>Clockwork Systems</t>
+        </is>
+      </c>
+      <c r="C456" s="5" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/clockworksystems/jobs/58...</t>
+        </is>
+      </c>
+      <c r="D456" s="6" t="inlineStr">
+        <is>
+          <t>shortlisted</t>
+        </is>
+      </c>
+      <c r="E456" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="F456" s="4" t="inlineStr">
+        <is>
+          <t>Auto-Shortlisted (Protected Title)</t>
+        </is>
+      </c>
+      <c r="G456" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-07T02:20:26.166785</t>
+        </is>
+      </c>
+      <c r="H456" s="7" t="inlineStr">
+        <is>
+          <t>➜ Apply</t>
+        </is>
+      </c>
+    </row>
+    <row r="457" ht="28" customHeight="1">
+      <c r="A457" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineer Intern</t>
+        </is>
+      </c>
+      <c r="B457" s="4" t="inlineStr">
+        <is>
+          <t>Centerfield</t>
+        </is>
+      </c>
+      <c r="C457" s="5" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/centerfield/3bcb68d6-1d15-4554-b...</t>
+        </is>
+      </c>
+      <c r="D457" s="6" t="inlineStr">
+        <is>
+          <t>shortlisted</t>
+        </is>
+      </c>
+      <c r="E457" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="F457" s="4" t="inlineStr">
+        <is>
+          <t>Auto-Shortlisted (Protected Title)</t>
+        </is>
+      </c>
+      <c r="G457" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-07T02:20:26.166785</t>
+        </is>
+      </c>
+      <c r="H457" s="7" t="inlineStr">
+        <is>
+          <t>➜ Apply</t>
+        </is>
+      </c>
+    </row>
+    <row r="458" ht="28" customHeight="1">
+      <c r="A458" s="8" t="inlineStr">
+        <is>
+          <t>Intern - Data Science</t>
+        </is>
+      </c>
+      <c r="B458" s="9" t="inlineStr">
+        <is>
+          <t>Kodiak Robotics</t>
+        </is>
+      </c>
+      <c r="C458" s="10" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/kodiak/jobs/4174629009</t>
+        </is>
+      </c>
+      <c r="D458" s="11" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="E458" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F458" s="9" t="inlineStr">
+        <is>
+          <t>Rejected: Found dealbreaker terms in JD (phd)</t>
+        </is>
+      </c>
+      <c r="G458" s="9" t="inlineStr">
+        <is>
+          <t>2026-03-07T02:20:26.166785</t>
+        </is>
+      </c>
+      <c r="H458" s="7" t="inlineStr">
+        <is>
+          <t>➜ Apply</t>
+        </is>
+      </c>
+    </row>
+    <row r="459" ht="28" customHeight="1">
+      <c r="A459" s="8" t="inlineStr">
+        <is>
+          <t>Intern - Artificial Intelligence/Machine Learning</t>
+        </is>
+      </c>
+      <c r="B459" s="9" t="inlineStr">
+        <is>
+          <t>Kodiak Robotics</t>
+        </is>
+      </c>
+      <c r="C459" s="10" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/kodiak/jobs/4174469009</t>
+        </is>
+      </c>
+      <c r="D459" s="11" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="E459" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F459" s="9" t="inlineStr">
+        <is>
+          <t>Rejected: Found dealbreaker terms in JD (ph.d)</t>
+        </is>
+      </c>
+      <c r="G459" s="9" t="inlineStr">
+        <is>
+          <t>2026-03-07T02:20:26.166785</t>
+        </is>
+      </c>
+      <c r="H459" s="7" t="inlineStr">
+        <is>
+          <t>➜ Apply</t>
+        </is>
+      </c>
+    </row>
+    <row r="460" ht="28" customHeight="1">
+      <c r="A460" s="8" t="inlineStr">
+        <is>
+          <t>Distribution Operations Engineering Intern</t>
+        </is>
+      </c>
+      <c r="B460" s="9" t="inlineStr">
+        <is>
+          <t>PG&amp;E</t>
+        </is>
+      </c>
+      <c r="C460" s="10" t="inlineStr">
+        <is>
+          <t>https://careers.pge.com/job/Rocklin-Distribution-Operatio...</t>
+        </is>
+      </c>
+      <c r="D460" s="11" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="E460" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="F460" s="9" t="inlineStr">
+        <is>
+          <t>The job is explicitly for an Internship, so no auto-reject occurs. The job requires 3-4 years of experience, which deducts -2. The job is in the Administrative/Clerical category, which does not apply the domain penalty. The candidate's experience and skills align well with the job requirements, but the job does not explicitly require any core AI/ML technologies, so no core tech mismatch penalty applies. The candidate's visa status is a mismatch, which deducts -4. The role does not match the candidate's target roles exactly, so no role relevance bonus applies.</t>
+        </is>
+      </c>
+      <c r="G460" s="9" t="inlineStr">
+        <is>
+          <t>2026-03-07T02:20:26.166785</t>
+        </is>
+      </c>
+      <c r="H460" s="7" t="inlineStr">
+        <is>
+          <t>➜ Apply</t>
+        </is>
+      </c>
+    </row>
+    <row r="461" ht="28" customHeight="1">
+      <c r="A461" s="3" t="inlineStr">
+        <is>
+          <t>Software Developer Intern/Co-op</t>
+        </is>
+      </c>
+      <c r="B461" s="4" t="inlineStr">
+        <is>
+          <t>Nokia</t>
+        </is>
+      </c>
+      <c r="C461" s="5" t="inlineStr">
+        <is>
+          <t>https://fa-evmr-saasfaprod1.fa.ocs.oraclecloud.com/hcmUI/...</t>
+        </is>
+      </c>
+      <c r="D461" s="6" t="inlineStr">
+        <is>
+          <t>shortlisted</t>
+        </is>
+      </c>
+      <c r="E461" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="F461" s="4" t="inlineStr">
+        <is>
+          <t>The job does not explicitly require US Citizenship or Security Clearance, so no auto-reject. The job requires 4+ months experience, which is 3-4 years, so -2. The job does not explicitly require 5+ years of experience, so no further deductions for experience gap. There are no core tech stack mismatches as the candidate has experience with Python, Java, JavaScript, Go, React, and other relevant technologies. The job is in the tech domain, so no domain penalty. The role title matches the candidate's target roles exactly, so +1. The score is 8, which is above the threshold of 6, so no further adjustments needed.</t>
+        </is>
+      </c>
+      <c r="G461" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-07T02:20:26.166785</t>
+        </is>
+      </c>
+      <c r="H461" s="7" t="inlineStr">
+        <is>
+          <t>➜ Apply</t>
+        </is>
+      </c>
+    </row>
+    <row r="462" ht="28" customHeight="1">
+      <c r="A462" s="3" t="inlineStr">
+        <is>
+          <t>Software Application Engineering Intern</t>
+        </is>
+      </c>
+      <c r="B462" s="4" t="inlineStr">
+        <is>
+          <t>Axiom Space</t>
+        </is>
+      </c>
+      <c r="C462" s="5" t="inlineStr">
+        <is>
+          <t>https://axiomspace.wd5.myworkdayjobs.com/External_Career_...</t>
+        </is>
+      </c>
+      <c r="D462" s="6" t="inlineStr">
+        <is>
+          <t>shortlisted</t>
+        </is>
+      </c>
+      <c r="E462" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="F462" s="4" t="inlineStr">
+        <is>
+          <t>The job is an internship, so no auto-reject applies. The candidate has relevant experience in Full Stack Development, AI Agents, LLM pipelines, Machine Learning, and Software Engineering, which matches the job requirements. The candidate's key skills include Python, Java, C++, TypeScript, JavaScript, SQL, Go, React, Next.js, Node.js, FastAPI, and various AI/ML libraries, which are all relevant. The job does not explicitly require US Citizenship or Security Clearance, and it is an internship, so no experience gap deduction applies. The domain is software engineering, which has a domain penalty of -0. The role title matches the candidate's target roles, so a +1 bonus is applied. The score is 8, which meets the candidate's score threshold of 6.</t>
+        </is>
+      </c>
+      <c r="G462" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-07T02:20:26.166785</t>
+        </is>
+      </c>
+      <c r="H462" s="7" t="inlineStr">
+        <is>
+          <t>➜ Apply</t>
+        </is>
+      </c>
+    </row>
+    <row r="463" ht="28" customHeight="1">
+      <c r="A463" s="3" t="inlineStr">
+        <is>
+          <t>Research Engineer</t>
+        </is>
+      </c>
+      <c r="B463" s="4" t="inlineStr">
+        <is>
+          <t>Snap</t>
+        </is>
+      </c>
+      <c r="C463" s="5" t="inlineStr">
+        <is>
+          <t>https://wd1.myworkdaysite.com/recruiting/snapchat/snap/jo...</t>
+        </is>
+      </c>
+      <c r="D463" s="6" t="inlineStr">
+        <is>
+          <t>shortlisted</t>
+        </is>
+      </c>
+      <c r="E463" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="F463" s="4" t="inlineStr">
+        <is>
+          <t>The job title is 'Research Engineer' which is not explicitly a senior role, so no auto-reject occurs. The job does not explicitly require US Citizenship or Security Clearance. The candidate is a Master's student, so the experience gap is not applicable. The job does not mention any specific core technologies that the candidate is missing. The domain is not finance, banking, or non-tech, so no domain penalty applies. The role title does not exactly match the candidate's target roles, but it involves AI/ML work, which adds a +1. The score is 8, which is above the candidate's threshold of 6, and the job does not require 5+ years of experience, so no deep keyword weaving is necessary.</t>
+        </is>
+      </c>
+      <c r="G463" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-07T02:20:26.166785</t>
+        </is>
+      </c>
+      <c r="H463" s="7" t="inlineStr">
+        <is>
+          <t>➜ Apply</t>
+        </is>
+      </c>
+    </row>
+    <row r="464" ht="28" customHeight="1">
+      <c r="A464" s="3" t="inlineStr">
+        <is>
+          <t>Career Opportunities</t>
+        </is>
+      </c>
+      <c r="B464" s="4" t="inlineStr">
+        <is>
+          <t>Kiongroup</t>
+        </is>
+      </c>
+      <c r="C464" s="5" t="inlineStr">
+        <is>
+          <t>https://kiongroup.wd3.myworkdayjobs.com/en-US/KION_SCS/jo...</t>
+        </is>
+      </c>
+      <c r="D464" s="6" t="inlineStr">
+        <is>
+          <t>shortlisted</t>
+        </is>
+      </c>
+      <c r="E464" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="F464" s="4" t="inlineStr">
+        <is>
+          <t>The job does not explicitly require US Citizenship or Security Clearance, so no auto-reject. The job is for a Software Engineer Intern, which matches the candidate's target roles, so no experience gap. The job does not explicitly list any core tech stack requirements, so no core tech stack mismatch. The job is in the tech domain, so no domain penalty. The job title matches the candidate's target roles, so a +1 is added. The score is 8, which meets the candidate's score threshold of 6.</t>
+        </is>
+      </c>
+      <c r="G464" s="4" t="inlineStr"/>
+      <c r="H464" s="7" t="inlineStr">
+        <is>
+          <t>➜ Apply</t>
+        </is>
+      </c>
+    </row>
+    <row r="465" ht="28" customHeight="1">
+      <c r="A465" s="3" t="inlineStr">
+        <is>
+          <t>If you run toward knowledge and problem-solving, join us</t>
+        </is>
+      </c>
+      <c r="B465" s="4" t="inlineStr">
+        <is>
+          <t>Careers</t>
+        </is>
+      </c>
+      <c r="C465" s="5" t="inlineStr">
+        <is>
+          <t>https://careers.netapp.com/job/-/-/27600/92444394544?jobP...</t>
+        </is>
+      </c>
+      <c r="D465" s="6" t="inlineStr">
+        <is>
+          <t>shortlisted</t>
+        </is>
+      </c>
+      <c r="E465" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="F465" s="4" t="inlineStr">
+        <is>
+          <t>The job is for a Software Engineer Intern, which is an internship, so it does not auto-reject. The job requires 3-4 years of experience, which deducts -2. The job does not explicitly require a specific core tech stack, so no deductions for core tech stack mismatch. The job is in the tech domain, so no domain penalty. The role title matches the candidate's target roles exactly, so a +1 is added. The candidate is enrolled in a Master of Computer Science program, which is relevant, and has experience in Full Stack Development, AI Agents, LLM pipelines, Machine Learning, and Software Engineering, which aligns well with the job requirements. The candidate's skills and experience are strong, but the job requires specific knowledge of distributed systems, cloud-native architectures, and CI/CD pipelines, which the candidate may not have extensive experience in, but the candidate is open to learning and has a strong foundation in computer science fundamentals. The candidate's visa status is a requirement for sponsorship, which is not explicitly mentioned as a negative factor in the rubric.</t>
+        </is>
+      </c>
+      <c r="G465" s="4" t="inlineStr"/>
+      <c r="H465" s="7" t="inlineStr">
+        <is>
+          <t>➜ Apply</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H314"/>
+  <autoFilter ref="A1:H465"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H2" r:id="rId2"/>
@@ -13751,6 +19783,308 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H313" r:id="rId624"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C314" r:id="rId625"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H314" r:id="rId626"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C315" r:id="rId627"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H315" r:id="rId628"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C316" r:id="rId629"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H316" r:id="rId630"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C317" r:id="rId631"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H317" r:id="rId632"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C318" r:id="rId633"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H318" r:id="rId634"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C319" r:id="rId635"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H319" r:id="rId636"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C320" r:id="rId637"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H320" r:id="rId638"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C321" r:id="rId639"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H321" r:id="rId640"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C322" r:id="rId641"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H322" r:id="rId642"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C323" r:id="rId643"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H323" r:id="rId644"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C324" r:id="rId645"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H324" r:id="rId646"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C325" r:id="rId647"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H325" r:id="rId648"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C326" r:id="rId649"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H326" r:id="rId650"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C327" r:id="rId651"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H327" r:id="rId652"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C328" r:id="rId653"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H328" r:id="rId654"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C329" r:id="rId655"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H329" r:id="rId656"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C330" r:id="rId657"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H330" r:id="rId658"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C331" r:id="rId659"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H331" r:id="rId660"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C332" r:id="rId661"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H332" r:id="rId662"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C333" r:id="rId663"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H333" r:id="rId664"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C334" r:id="rId665"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H334" r:id="rId666"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C335" r:id="rId667"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H335" r:id="rId668"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C336" r:id="rId669"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H336" r:id="rId670"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C337" r:id="rId671"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H337" r:id="rId672"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C338" r:id="rId673"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H338" r:id="rId674"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C339" r:id="rId675"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H339" r:id="rId676"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C340" r:id="rId677"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H340" r:id="rId678"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C341" r:id="rId679"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H341" r:id="rId680"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C342" r:id="rId681"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H342" r:id="rId682"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C343" r:id="rId683"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H343" r:id="rId684"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C344" r:id="rId685"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H344" r:id="rId686"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C345" r:id="rId687"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H345" r:id="rId688"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C346" r:id="rId689"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H346" r:id="rId690"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C347" r:id="rId691"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H347" r:id="rId692"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C348" r:id="rId693"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H348" r:id="rId694"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C349" r:id="rId695"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H349" r:id="rId696"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C350" r:id="rId697"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H350" r:id="rId698"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C351" r:id="rId699"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H351" r:id="rId700"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C352" r:id="rId701"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H352" r:id="rId702"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C353" r:id="rId703"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H353" r:id="rId704"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C354" r:id="rId705"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H354" r:id="rId706"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C355" r:id="rId707"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H355" r:id="rId708"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C356" r:id="rId709"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H356" r:id="rId710"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C357" r:id="rId711"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H357" r:id="rId712"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C358" r:id="rId713"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H358" r:id="rId714"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C359" r:id="rId715"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H359" r:id="rId716"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C360" r:id="rId717"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H360" r:id="rId718"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C361" r:id="rId719"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H361" r:id="rId720"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C362" r:id="rId721"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H362" r:id="rId722"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C363" r:id="rId723"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H363" r:id="rId724"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C364" r:id="rId725"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H364" r:id="rId726"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C365" r:id="rId727"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H365" r:id="rId728"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C366" r:id="rId729"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H366" r:id="rId730"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C367" r:id="rId731"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H367" r:id="rId732"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C368" r:id="rId733"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H368" r:id="rId734"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C369" r:id="rId735"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H369" r:id="rId736"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C370" r:id="rId737"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H370" r:id="rId738"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C371" r:id="rId739"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H371" r:id="rId740"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C372" r:id="rId741"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H372" r:id="rId742"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C373" r:id="rId743"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H373" r:id="rId744"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C374" r:id="rId745"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H374" r:id="rId746"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C375" r:id="rId747"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H375" r:id="rId748"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C376" r:id="rId749"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H376" r:id="rId750"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C377" r:id="rId751"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H377" r:id="rId752"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C378" r:id="rId753"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H378" r:id="rId754"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C379" r:id="rId755"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H379" r:id="rId756"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C380" r:id="rId757"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H380" r:id="rId758"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C381" r:id="rId759"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H381" r:id="rId760"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C382" r:id="rId761"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H382" r:id="rId762"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C383" r:id="rId763"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H383" r:id="rId764"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C384" r:id="rId765"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H384" r:id="rId766"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C385" r:id="rId767"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H385" r:id="rId768"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C386" r:id="rId769"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H386" r:id="rId770"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C387" r:id="rId771"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H387" r:id="rId772"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C388" r:id="rId773"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H388" r:id="rId774"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C389" r:id="rId775"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H389" r:id="rId776"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C390" r:id="rId777"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H390" r:id="rId778"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C391" r:id="rId779"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H391" r:id="rId780"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C392" r:id="rId781"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H392" r:id="rId782"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C393" r:id="rId783"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H393" r:id="rId784"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C394" r:id="rId785"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H394" r:id="rId786"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C395" r:id="rId787"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H395" r:id="rId788"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C396" r:id="rId789"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H396" r:id="rId790"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C397" r:id="rId791"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H397" r:id="rId792"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C398" r:id="rId793"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H398" r:id="rId794"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C399" r:id="rId795"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H399" r:id="rId796"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C400" r:id="rId797"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H400" r:id="rId798"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C401" r:id="rId799"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H401" r:id="rId800"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C402" r:id="rId801"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H402" r:id="rId802"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C403" r:id="rId803"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H403" r:id="rId804"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C404" r:id="rId805"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H404" r:id="rId806"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C405" r:id="rId807"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H405" r:id="rId808"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C406" r:id="rId809"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H406" r:id="rId810"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C407" r:id="rId811"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H407" r:id="rId812"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C408" r:id="rId813"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H408" r:id="rId814"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C409" r:id="rId815"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H409" r:id="rId816"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C410" r:id="rId817"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H410" r:id="rId818"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C411" r:id="rId819"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H411" r:id="rId820"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C412" r:id="rId821"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H412" r:id="rId822"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C413" r:id="rId823"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H413" r:id="rId824"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C414" r:id="rId825"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H414" r:id="rId826"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C415" r:id="rId827"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H415" r:id="rId828"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C416" r:id="rId829"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H416" r:id="rId830"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C417" r:id="rId831"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H417" r:id="rId832"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C418" r:id="rId833"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H418" r:id="rId834"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C419" r:id="rId835"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H419" r:id="rId836"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C420" r:id="rId837"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H420" r:id="rId838"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C421" r:id="rId839"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H421" r:id="rId840"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C422" r:id="rId841"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H422" r:id="rId842"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C423" r:id="rId843"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H423" r:id="rId844"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C424" r:id="rId845"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H424" r:id="rId846"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C425" r:id="rId847"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H425" r:id="rId848"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C426" r:id="rId849"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H426" r:id="rId850"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C427" r:id="rId851"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H427" r:id="rId852"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C428" r:id="rId853"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H428" r:id="rId854"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C429" r:id="rId855"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H429" r:id="rId856"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C430" r:id="rId857"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H430" r:id="rId858"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C431" r:id="rId859"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H431" r:id="rId860"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C432" r:id="rId861"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H432" r:id="rId862"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C433" r:id="rId863"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H433" r:id="rId864"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C434" r:id="rId865"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H434" r:id="rId866"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C435" r:id="rId867"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H435" r:id="rId868"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C436" r:id="rId869"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H436" r:id="rId870"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C437" r:id="rId871"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H437" r:id="rId872"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C438" r:id="rId873"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H438" r:id="rId874"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C439" r:id="rId875"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H439" r:id="rId876"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C440" r:id="rId877"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H440" r:id="rId878"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C441" r:id="rId879"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H441" r:id="rId880"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C442" r:id="rId881"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H442" r:id="rId882"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C443" r:id="rId883"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H443" r:id="rId884"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C444" r:id="rId885"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H444" r:id="rId886"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C445" r:id="rId887"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H445" r:id="rId888"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C446" r:id="rId889"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H446" r:id="rId890"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C447" r:id="rId891"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H447" r:id="rId892"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C448" r:id="rId893"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H448" r:id="rId894"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C449" r:id="rId895"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H449" r:id="rId896"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C450" r:id="rId897"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H450" r:id="rId898"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C451" r:id="rId899"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H451" r:id="rId900"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C452" r:id="rId901"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H452" r:id="rId902"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C453" r:id="rId903"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H453" r:id="rId904"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C454" r:id="rId905"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H454" r:id="rId906"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C455" r:id="rId907"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H455" r:id="rId908"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C456" r:id="rId909"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H456" r:id="rId910"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C457" r:id="rId911"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H457" r:id="rId912"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C458" r:id="rId913"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H458" r:id="rId914"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C459" r:id="rId915"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H459" r:id="rId916"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C460" r:id="rId917"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H460" r:id="rId918"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C461" r:id="rId919"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H461" r:id="rId920"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C462" r:id="rId921"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H462" r:id="rId922"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C463" r:id="rId923"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H463" r:id="rId924"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C464" r:id="rId925"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H464" r:id="rId926"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C465" r:id="rId927"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H465" r:id="rId928"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
